--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,19 +737,19 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1862
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
@@ -761,31 +761,31 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
-</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -803,13 +803,13 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
@@ -821,7 +821,7 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -833,13 +833,13 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1689
+          <t xml:space="preserve">6839
 </t>
         </is>
       </c>
@@ -857,7 +857,7 @@
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -869,16 +869,11 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8118
-</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -894,7 +889,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4035
+          <t xml:space="preserve">435
 </t>
         </is>
       </c>
@@ -904,15 +899,10 @@
 </t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
+      <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
@@ -922,15 +912,10 @@
 </t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
+      <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -946,9 +931,9 @@
 </t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
@@ -960,13 +945,13 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">2920
 </t>
         </is>
       </c>
@@ -976,15 +961,15 @@
 </t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">326
+      <c r="Q5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -996,46 +981,41 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1566
+          <t xml:space="preserve">566
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
-      <c r="X5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
-</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="n"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>2</t>
@@ -1051,19 +1031,20 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4223
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">48
+13
 </t>
         </is>
       </c>
@@ -1081,19 +1062,19 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -1123,7 +1104,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">1060
 </t>
         </is>
       </c>
@@ -1147,25 +1128,25 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">552
+          <t xml:space="preserve">528
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1177,19 +1158,20 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">664
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">132
+</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1207,30 +1189,27 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>43351</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">347
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">486860108728
+171171808
+</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -1242,47 +1221,42 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">351
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -1294,13 +1268,13 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -1312,34 +1286,29 @@
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="W7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">662
 </t>
         </is>
       </c>
+      <c r="Y7" s="3" t="n"/>
       <c r="Z7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">138
@@ -1361,13 +1330,14 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2990
+          <t xml:space="preserve">2926
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t xml:space="preserve">348
+</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1384,13 +1354,13 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -1402,12 +1372,13 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">40
+</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">369
 </t>
         </is>
       </c>
@@ -1419,85 +1390,85 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">965
+</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">409
-</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">965
-</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">974
-</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -1516,19 +1487,19 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17835
+          <t xml:space="preserve">7835
 </t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1648
+          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">969
+          <t xml:space="preserve">9629
 </t>
         </is>
       </c>
@@ -1546,7 +1517,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">824
 </t>
         </is>
       </c>
@@ -1558,7 +1529,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">2785
 </t>
         </is>
       </c>
@@ -1570,43 +1541,43 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1002
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">92926
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18945
+          <t xml:space="preserve">945
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1496
+          <t xml:space="preserve">496
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
@@ -1618,13 +1589,13 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2299
+          <t xml:space="preserve">22929
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -1636,23 +1607,23 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">1335
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1335
-</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3888
-</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="n"/>
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="n"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1668,19 +1639,19 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3567
+          <t xml:space="preserve">367
 </t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
+          <t xml:space="preserve">339
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1692,13 +1663,13 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">1 36
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -1714,7 +1685,12 @@
 </t>
         </is>
       </c>
-      <c r="K10" s="3" t="n"/>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">200
@@ -1723,35 +1699,35 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="N10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
-        </is>
-      </c>
-      <c r="R10" s="8" t="inlineStr">
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">244
 </t>
@@ -1759,49 +1735,49 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="W10" s="8" t="inlineStr">
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">234
 </t>
         </is>
       </c>
-      <c r="X10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">267
+      <c r="X10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">416
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -1824,22 +1800,21 @@
 </t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1850,31 +1825,29 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">866
+          <t>181</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -1884,15 +1857,15 @@
 </t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1245
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0923
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
@@ -1902,19 +1875,18 @@
 </t>
         </is>
       </c>
-      <c r="Q11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">299
-</t>
-        </is>
-      </c>
-      <c r="R11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="S11" s="8" t="inlineStr">
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>9949</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">298
 </t>
@@ -1922,40 +1894,33 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">706
-</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">271
-</t>
-        </is>
-      </c>
-      <c r="W11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">660
+</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">840
-</t>
-        </is>
-      </c>
+          <t>3403</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="n"/>
       <c r="Z11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">83
@@ -1977,7 +1942,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3471
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
@@ -1995,13 +1960,14 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">22
+191
 </t>
         </is>
       </c>
@@ -2017,15 +1983,15 @@
 </t>
         </is>
       </c>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">446
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2043,19 +2009,20 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">979
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">05
+711
 </t>
         </is>
       </c>
@@ -2067,55 +2034,55 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271
+</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271
+</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">249
 </t>
         </is>
       </c>
-      <c r="S12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">271
-</t>
-        </is>
-      </c>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">578
-</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="W12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">767
+          <t xml:space="preserve">22927
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">572
 </t>
         </is>
       </c>
@@ -2134,25 +2101,25 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14286
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">966
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -2164,7 +2131,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -2176,7 +2143,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2186,9 +2153,9 @@
 </t>
         </is>
       </c>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -2206,13 +2173,13 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -2224,55 +2191,54 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">246
 </t>
         </is>
       </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="T13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">527
-</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
-      <c r="W13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="X13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">293
+      <c r="X13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">727
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">776
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -2291,19 +2257,19 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903
+          <t xml:space="preserve">903
 </t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">607
+</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -2321,7 +2287,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
@@ -2333,52 +2299,52 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">821
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">973
+</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">224
 </t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">973
-</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">824
-</t>
-        </is>
-      </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">211
@@ -2387,13 +2353,13 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">527
 </t>
         </is>
       </c>
@@ -2405,20 +2371,14 @@
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">280
+</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="n"/>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -2448,7 +2408,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3596
+          <t xml:space="preserve">356
 </t>
         </is>
       </c>
@@ -2458,9 +2418,9 @@
 </t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">088
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -2470,15 +2430,15 @@
 </t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4196
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -2496,22 +2456,22 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">216
 </t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">258
@@ -2520,7 +2480,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">10060
 </t>
         </is>
       </c>
@@ -2544,13 +2504,13 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">617
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -2562,26 +2522,25 @@
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">731
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
@@ -2605,19 +2564,19 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15912
+          <t xml:space="preserve">15992
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">1529
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1055
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -2635,13 +2594,13 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
+          <t xml:space="preserve">3922
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -2651,11 +2610,21 @@
 </t>
         </is>
       </c>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">368
+</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1095
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -2667,19 +2636,19 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4901
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1487
+          <t xml:space="preserve">482
 </t>
         </is>
       </c>
@@ -2691,25 +2660,25 @@
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1361
+          <t xml:space="preserve">361
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3318
+          <t xml:space="preserve">617
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">766
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1337
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -2721,17 +2690,22 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1425
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4074
-</t>
-        </is>
-      </c>
-      <c r="Z16" s="3" t="n"/>
+          <t xml:space="preserve">476
+</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2747,7 +2721,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3182
+          <t xml:space="preserve">34182
 </t>
         </is>
       </c>
@@ -2759,7 +2733,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
@@ -2771,7 +2745,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -2799,9 +2773,9 @@
 </t>
         </is>
       </c>
-      <c r="L17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -2819,60 +2793,61 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="S17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
+          <t xml:space="preserve">364
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">664
-</t>
-        </is>
-      </c>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">3318
+</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">453
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">337
 </t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>941</t>
-        </is>
-      </c>
-      <c r="X17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="X17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">425
 </t>
         </is>
       </c>
@@ -2884,7 +2859,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">344
 </t>
         </is>
       </c>
@@ -2903,7 +2878,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3680
+          <t xml:space="preserve">3686
 </t>
         </is>
       </c>
@@ -2919,7 +2894,7 @@
 </t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">267
 </t>
@@ -2927,13 +2902,13 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">064
 </t>
         </is>
       </c>
@@ -2945,11 +2920,15 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="n"/>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">76
+</t>
+        </is>
+      </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">221
@@ -2958,19 +2937,18 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
+          <t xml:space="preserve">973
 </t>
         </is>
       </c>
@@ -2986,7 +2964,7 @@
 </t>
         </is>
       </c>
-      <c r="R18" s="8" t="inlineStr">
+      <c r="R18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">252
 </t>
@@ -2994,17 +2972,17 @@
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">3
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
+          <t xml:space="preserve">664
+</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">200
 </t>
@@ -3012,31 +2990,31 @@
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">467
+</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">285
 </t>
         </is>
       </c>
-      <c r="W18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="X18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">717
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -3055,8 +3033,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2656
-</t>
+          <t>856</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -3067,7 +3044,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3085,7 +3062,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -3103,43 +3080,44 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">662
+1254
 </t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">976
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="Q19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
@@ -3151,48 +3129,50 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">737
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>214</t>
+          <t xml:space="preserve">290
+</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">10
+</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3220,21 +3200,21 @@
 </t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">415
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -3252,31 +3232,31 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">662
+1254
 </t>
         </is>
       </c>
@@ -3288,8 +3268,7 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -3300,19 +3279,19 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">623
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -3324,31 +3303,31 @@
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
@@ -3379,13 +3358,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
@@ -3415,7 +3394,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
@@ -3433,13 +3412,13 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
@@ -3463,13 +3442,13 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">712
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
@@ -3481,34 +3460,29 @@
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
-        </is>
-      </c>
-      <c r="W21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="X21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
+      <c r="W21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">438
+</t>
+        </is>
+      </c>
+      <c r="X21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7723
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="n"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -3542,19 +3516,19 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -3572,31 +3546,31 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -3620,52 +3594,47 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">893
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
-</t>
-        </is>
-      </c>
-      <c r="U22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">2126
+</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">723
+</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="n"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -3681,89 +3650,92 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17396
+          <t xml:space="preserve">7326
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">422999227
+1149 6
+</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1072
+</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1324
+</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">563
+</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4574532851
+12818
+</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1070
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1268
+</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">22
 </t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>037</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1324
-</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">503
-</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77
-</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">911
-</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14894
-</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1557
+          <t xml:space="preserve">557
 </t>
         </is>
       </c>
@@ -3775,46 +3747,50 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11468
+          <t xml:space="preserve">893
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3957
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>7924</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1344
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1203
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>14081</t>
+          <t xml:space="preserve">297
+</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>39404</t>
+          <t xml:space="preserve">260
+</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">24
+78
 </t>
         </is>
       </c>
@@ -3833,13 +3809,13 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3439
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
+          <t xml:space="preserve">575
 </t>
         </is>
       </c>
@@ -3851,13 +3827,13 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -3869,7 +3845,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -3881,37 +3857,37 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="L24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">082
-</t>
-        </is>
-      </c>
-      <c r="M24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">070
-</t>
-        </is>
-      </c>
-      <c r="N24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">979
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -3923,55 +3899,56 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">651
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="V24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">408
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
+          <t xml:space="preserve">3990
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">24
+78
 </t>
         </is>
       </c>
@@ -3990,20 +3967,19 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1067
+          <t xml:space="preserve">067
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">315
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -4014,7 +3990,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -4026,111 +4002,107 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">24127
+210
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>9861</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">779717
+1791818
+</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7783
+181186
+</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6541
+</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41
+</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">22
 </t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">979
-</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="R25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1461
-</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">844
-</t>
-        </is>
-      </c>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t>2441</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
-      <c r="X25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="n"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -4152,7 +4124,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
@@ -4170,7 +4142,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -4182,111 +4154,105 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t xml:space="preserve">214
+</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">080
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">268
 </t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12970
-</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
-</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
-      <c r="T26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="U26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="W26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">271
-</t>
-        </is>
-      </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">877
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">872
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="n"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -4308,13 +4274,13 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -4326,7 +4292,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">399
 </t>
         </is>
       </c>
@@ -4338,13 +4304,14 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">08
+34
 </t>
         </is>
       </c>
@@ -4356,7 +4323,7 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -4366,9 +4333,9 @@
 </t>
         </is>
       </c>
-      <c r="N27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -4380,7 +4347,7 @@
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -4392,58 +4359,53 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
-      </c>
-      <c r="Z27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="n"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -4459,14 +4421,13 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29907
+          <t xml:space="preserve">2907
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -4481,7 +4442,7 @@
 </t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">113
 </t>
@@ -4507,11 +4468,11 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">209
 </t>
@@ -4525,19 +4486,19 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -4555,13 +4516,13 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
@@ -4573,19 +4534,18 @@
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -4597,7 +4557,7 @@
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -4616,36 +4576,36 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>34681</t>
+          <t>865</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
+          <t xml:space="preserve">368
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -4669,25 +4629,25 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">506
 </t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1953
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
@@ -4697,62 +4657,63 @@
 </t>
         </is>
       </c>
-      <c r="Q29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">853
 </t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>361</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">726
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4771,37 +4732,37 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10562
+          <t xml:space="preserve">0566
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1452
+          <t xml:space="preserve">315
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">032
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
+          <t xml:space="preserve">4280
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">966
 </t>
         </is>
       </c>
@@ -4813,7 +4774,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -4825,25 +4786,25 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1065
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11592
+          <t xml:space="preserve">1526
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4876
+          <t xml:space="preserve">953
 </t>
         </is>
       </c>
@@ -4855,7 +4816,7 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11858
+          <t xml:space="preserve">358
 </t>
         </is>
       </c>
@@ -4867,25 +4828,25 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1409
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3968
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -4897,19 +4858,19 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1358
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -4934,7 +4895,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">452
 </t>
         </is>
       </c>
@@ -4946,61 +4907,61 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9
+</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11171
+</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">248
 </t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">966
-</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">388
-</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="N31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
+          <t xml:space="preserve">4826
 </t>
         </is>
       </c>
@@ -5012,7 +4973,7 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">972
 </t>
         </is>
       </c>
@@ -5022,50 +4983,51 @@
 </t>
         </is>
       </c>
-      <c r="S31" s="3" t="inlineStr">
+      <c r="S31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">409
+</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3968
+</t>
+        </is>
+      </c>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">381
+</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="X31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">282
 </t>
         </is>
       </c>
-      <c r="T31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">794
-</t>
-        </is>
-      </c>
-      <c r="U31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
-      <c r="V31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="W31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="X31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">4417
+</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
@@ -5090,7 +5052,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -5102,30 +5064,31 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>9521</t>
+          <t xml:space="preserve">256
+</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="J32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -5135,7 +5098,7 @@
 </t>
         </is>
       </c>
-      <c r="L32" s="8" t="inlineStr">
+      <c r="L32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">201
 </t>
@@ -5143,85 +5106,84 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="N32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">785
 </t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
-        </is>
-      </c>
-      <c r="R32" s="8" t="inlineStr">
+          <t>341</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">439
+</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">249
 </t>
         </is>
       </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="T32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">610
-</t>
-        </is>
-      </c>
-      <c r="U32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="V32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">974
-</t>
-        </is>
-      </c>
-      <c r="W32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
@@ -5240,26 +5202,25 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2133
+          <t xml:space="preserve">2423
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -5268,26 +5229,27 @@
 </t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t xml:space="preserve">23
+</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">516
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -5297,21 +5259,20 @@
 </t>
         </is>
       </c>
-      <c r="M33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0214
-</t>
-        </is>
-      </c>
-      <c r="N33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1600
 </t>
         </is>
       </c>
@@ -5323,36 +5284,37 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
-        </is>
-      </c>
-      <c r="R33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">846
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t xml:space="preserve">75
+</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">709
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -5364,19 +5326,19 @@
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">2862 2
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">746
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -5401,17 +5363,18 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+214
+</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">267
 </t>
@@ -5425,13 +5388,14 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t xml:space="preserve">10
+</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -5442,43 +5406,43 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">859
+</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">02
 </t>
         </is>
       </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="N34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11990
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
@@ -5490,13 +5454,13 @@
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -5508,29 +5472,32 @@
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
-        </is>
-      </c>
-      <c r="W34" s="8" t="inlineStr">
-        <is>
-          <t>1382484</t>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t xml:space="preserve">46
+</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">65
+</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5554,139 +5521,139 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">319
+</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">060
+</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">859
+</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">311
 </t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">978
-</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="Q35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311
-</t>
-        </is>
-      </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">613
+          <t xml:space="preserve">694
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
-        </is>
-      </c>
-      <c r="W35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">466
+          <t xml:space="preserve">723
+</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -5711,88 +5678,88 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">311
+</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">265
+</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">306
+</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">975
+</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">321
 </t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">265
-</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">306
-</t>
-        </is>
-      </c>
-      <c r="L36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">410
-</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9725
-</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="Q36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321
-</t>
-        </is>
-      </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">260
@@ -5801,7 +5768,7 @@
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -5811,19 +5778,19 @@
 </t>
         </is>
       </c>
-      <c r="U36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="W36" s="8" t="inlineStr">
+          <t xml:space="preserve">278
+</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">246
 </t>
@@ -5837,14 +5804,12 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">794
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5862,25 +5827,26 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16937
+          <t xml:space="preserve">6937
 </t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1554
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>18871</t>
+          <t xml:space="preserve">1287
+</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -5897,13 +5863,12 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -5915,25 +5880,25 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1060
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10159
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11927
+          <t xml:space="preserve">427
 </t>
         </is>
       </c>
@@ -5945,7 +5910,7 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1537
+          <t xml:space="preserve">537
 </t>
         </is>
       </c>
@@ -5957,7 +5922,8 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11431
+          <t xml:space="preserve">792798
+11811
 </t>
         </is>
       </c>
@@ -5969,36 +5935,38 @@
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">777
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1368
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">466
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
+          <t xml:space="preserve">7260
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0011
+          <t xml:space="preserve">82745857727
+12119
 </t>
         </is>
       </c>
@@ -6023,19 +5991,19 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -6047,19 +6015,19 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -6071,19 +6039,19 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="N38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">412
+</t>
+        </is>
+      </c>
+      <c r="M38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">410
+</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -6095,13 +6063,13 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
-      <c r="Q38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="Q38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">607
 </t>
         </is>
       </c>
@@ -6111,51 +6079,51 @@
 </t>
         </is>
       </c>
-      <c r="S38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286
+      <c r="S38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">431
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">650
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="V38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">874
-</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
-</t>
-        </is>
-      </c>
-      <c r="X38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">368
+</t>
+        </is>
+      </c>
+      <c r="W38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="X38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">982
+          <t xml:space="preserve">794
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
@@ -6174,103 +6142,99 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3325
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">310
+</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>901</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+111
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">319
 </t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="H39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
-      <c r="M39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="N39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">719
-</t>
-        </is>
-      </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -6282,37 +6246,37 @@
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">386
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -6331,13 +6295,14 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4537
-</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">7924
+265
+</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -6355,11 +6320,11 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="inlineStr">
+          <t xml:space="preserve">41
+</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">182
 </t>
@@ -6367,13 +6332,13 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -6391,13 +6356,14 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="N40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">269
+111
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -6409,7 +6375,7 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -6425,51 +6391,51 @@
 </t>
         </is>
       </c>
-      <c r="S40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">293
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">982
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -6488,13 +6454,14 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2656
+          <t xml:space="preserve">7924
+265
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
@@ -6504,7 +6471,7 @@
 </t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">256
 </t>
@@ -6516,32 +6483,33 @@
 </t>
         </is>
       </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>434</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -6551,9 +6519,9 @@
 </t>
         </is>
       </c>
-      <c r="N41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -6583,13 +6551,13 @@
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -6599,33 +6567,32 @@
 </t>
         </is>
       </c>
-      <c r="V41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -6648,7 +6615,7 @@
 </t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">316
 </t>
@@ -6668,41 +6635,41 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="M42" s="8" t="inlineStr">
+          <t xml:space="preserve">412
+</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">218
 </t>
@@ -6710,19 +6677,19 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -6740,49 +6707,49 @@
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">893
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">977
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -6801,13 +6768,13 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3722
+          <t xml:space="preserve">722
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
@@ -6819,7 +6786,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">857
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -6829,7 +6796,7 @@
 </t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
@@ -6837,7 +6804,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -6849,7 +6816,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6861,14 +6828,13 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">956
-</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
@@ -6891,13 +6857,13 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
@@ -6909,36 +6875,37 @@
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">847
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="W43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t xml:space="preserve">21
+</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">786
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -6963,103 +6930,103 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">300
+</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">283
+</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1060
+</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">326
 </t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">823
-</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1000
-</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">800
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">668
 </t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">621
 </t>
         </is>
       </c>
@@ -7071,31 +7038,31 @@
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">462
 </t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">841
 </t>
         </is>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -7114,142 +7081,133 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19016
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">021
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1561
+          <t xml:space="preserve">561
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">7283
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">7263
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18259
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">987
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59838
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
-</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="n"/>
+      <c r="S45" s="3" t="n"/>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t xml:space="preserve">4500
+</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">686
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t xml:space="preserve">3581
+</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1449
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>775</t>
+          <t xml:space="preserve">1725
+</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="n"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -7265,31 +7223,31 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2376
+          <t xml:space="preserve">376
 </t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">906
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -7311,22 +7269,27 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="n"/>
+      <c r="K46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">283
+</t>
+        </is>
+      </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">411
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -7338,7 +7301,7 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -7350,7 +7313,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -7362,25 +7325,25 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">750
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
       <c r="W46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">442
 </t>
         </is>
       </c>
@@ -7392,16 +7355,11 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,59 +737,58 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1862
 </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">202
 </t>
@@ -801,37 +800,32 @@
 </t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
+      <c r="N4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">834
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="n"/>
       <c r="R4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">241
 </t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="S4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">271
 </t>
@@ -839,11 +833,11 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6839
-</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
+          <t xml:space="preserve">689
+</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">122
 </t>
@@ -857,11 +851,11 @@
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="X4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">262
 </t>
@@ -869,11 +863,16 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="n"/>
+          <t xml:space="preserve">18118
+</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -889,30 +888,39 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">435
-</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+          <t xml:space="preserve">29038
+</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">326
 </t>
         </is>
       </c>
-      <c r="E5" s="3" t="n"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="n"/>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">35
@@ -927,13 +935,13 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -943,33 +951,33 @@
 </t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
+      <c r="N5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">326
+</t>
+        </is>
+      </c>
+      <c r="R5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -981,41 +989,45 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">566
+          <t xml:space="preserve">1566
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
+      <c r="W5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
+      <c r="X5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="n"/>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>2</t>
@@ -1031,20 +1043,19 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">14223
+</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">342
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-13
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -1060,27 +1071,27 @@
 </t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8726
 </t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -1104,19 +1115,19 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1060
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -1126,27 +1137,27 @@
 </t>
         </is>
       </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
+      <c r="S6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">528
-</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">29298
+</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -1158,20 +1169,19 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">1664
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1189,27 +1199,29 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">486860108728
-171171808
-</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n"/>
+          <t>47851</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
@@ -1221,94 +1233,105 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t xml:space="preserve">79
+</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="n"/>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1000
+</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">342
+</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">225
 </t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">342
-</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
+      <c r="S7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">506
-</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1206
+</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">265
+</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="W7" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="n"/>
+          <t xml:space="preserve">273
+</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1662
+</t>
+        </is>
+      </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">138
@@ -1330,19 +1353,19 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2926
-</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">348
-</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">806
+          <t xml:space="preserve">12990
+</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">346
+</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -1354,31 +1377,31 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">120
 </t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">369
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
@@ -1388,9 +1411,9 @@
 </t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -1402,67 +1425,67 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">1965
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">2980
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">019
 </t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">974
 </t>
         </is>
       </c>
@@ -1487,37 +1510,37 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7835
+          <t xml:space="preserve">117835
 </t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
+          <t xml:space="preserve">1648
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9629
+          <t xml:space="preserve">1969
 </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1308
+          <t xml:space="preserve">11308
 </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">679
+          <t xml:space="preserve">1619
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
@@ -1529,7 +1552,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2785
+          <t xml:space="preserve">1275
 </t>
         </is>
       </c>
@@ -1541,25 +1564,25 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1002
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92926
+          <t xml:space="preserve">1996
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">945
+          <t xml:space="preserve">14945
 </t>
         </is>
       </c>
@@ -1571,31 +1594,31 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">496
+          <t xml:space="preserve">1496
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
+          <t xml:space="preserve">1219
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1357
+          <t xml:space="preserve">11357
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22929
+          <t xml:space="preserve">3299
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">0960
 </t>
         </is>
       </c>
@@ -1607,20 +1630,25 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1335
+          <t xml:space="preserve">11168
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="n"/>
+          <t xml:space="preserve">11335
+</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13888
+</t>
+        </is>
+      </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">1416
 </t>
         </is>
       </c>
@@ -1639,19 +1667,19 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">367
-</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">339
+          <t xml:space="preserve">3567
+</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3930
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -1661,15 +1689,15 @@
 </t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 36
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -1685,13 +1713,8 @@
 </t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">200
 </t>
@@ -1699,19 +1722,19 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
@@ -1721,13 +1744,13 @@
 </t>
         </is>
       </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="inlineStr">
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">299
+</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">244
 </t>
@@ -1735,49 +1758,49 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="W10" s="3" t="inlineStr">
+          <t xml:space="preserve">1660
+</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
+      <c r="W10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">234
 </t>
         </is>
       </c>
-      <c r="X10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">888
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">798
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -1796,93 +1819,97 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2656
+          <t xml:space="preserve">12656
 </t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">601
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">28
 </t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>2459</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">100
+</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">209
 </t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">45
+      <c r="N11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">9273
 </t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>9949</t>
+          <t xml:space="preserve">299
+</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -1894,36 +1921,43 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">1706
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>3403</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="n"/>
+          <t xml:space="preserve">301
+</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6840
+</t>
+        </is>
+      </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
@@ -1942,99 +1976,97 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
+          <t xml:space="preserve">2471
+</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
+</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">318
 </t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-191
-</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">979
-</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78
-</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05
-711
-</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">318
-</t>
-        </is>
-      </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -2046,43 +2078,43 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">598
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">279
+</t>
+        </is>
+      </c>
+      <c r="W12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2846
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22927
+          <t xml:space="preserve">767
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
+          <t xml:space="preserve">1817
 </t>
         </is>
       </c>
@@ -2101,23 +2133,23 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
-</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">14286
+</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">266
 </t>
@@ -2131,31 +2163,31 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -2173,72 +2205,73 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">326
+</t>
+        </is>
+      </c>
+      <c r="R13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">527
+</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">280
 </t>
         </is>
       </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">326
-</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="T13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78
-</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="V13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79
-</t>
-        </is>
-      </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="X13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">727
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">776
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -2257,19 +2290,19 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">903
-</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">607
-</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1903
+</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">301
+</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -2285,9 +2318,9 @@
 </t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -2303,39 +2336,38 @@
 </t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">973
+          <t xml:space="preserve">1973
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
@@ -2351,15 +2383,15 @@
 </t>
         </is>
       </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
+      <c r="S14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">527
+          <t xml:space="preserve">1890
 </t>
         </is>
       </c>
@@ -2371,26 +2403,31 @@
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="n"/>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t>8343</t>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="X14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">1960
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>091</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2408,7 +2445,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
+          <t xml:space="preserve">3596
 </t>
         </is>
       </c>
@@ -2418,21 +2455,21 @@
 </t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">267
 </t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -2444,7 +2481,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -2456,13 +2493,13 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -2480,17 +2517,17 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10060
+          <t xml:space="preserve">11000
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="inlineStr">
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="Q15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">320
 </t>
@@ -2510,7 +2547,7 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">1617
 </t>
         </is>
       </c>
@@ -2522,30 +2559,31 @@
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="W15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="W15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">731
+</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
@@ -2564,25 +2602,25 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15992
+          <t xml:space="preserve">12912
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1529
+          <t xml:space="preserve">1579
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">11055
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1317
+          <t xml:space="preserve">51317
 </t>
         </is>
       </c>
@@ -2594,13 +2632,13 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3922
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">1115
 </t>
         </is>
       </c>
@@ -2618,25 +2656,25 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">11106
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">1095
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1307
+          <t xml:space="preserve">11307
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">274901
 </t>
         </is>
       </c>
@@ -2648,61 +2686,61 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">482
+          <t xml:space="preserve">1487
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">11219
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
+          <t xml:space="preserve">11361
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">617
+          <t xml:space="preserve">3318
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">1766
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">1337
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">11207
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">1625
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">476
+          <t xml:space="preserve">14074
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">344
 </t>
         </is>
       </c>
@@ -2721,7 +2759,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34182
+          <t xml:space="preserve">13182
 </t>
         </is>
       </c>
@@ -2733,133 +2771,128 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">263
+</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">297
+</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="S17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1664
+</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">153
+</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">267
+</t>
+        </is>
+      </c>
+      <c r="W17" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">241
 </t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">368
-</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="S17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">364
-</t>
-        </is>
-      </c>
-      <c r="T17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3318
-</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">453
-</t>
-        </is>
-      </c>
-      <c r="V17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">337
-</t>
-        </is>
-      </c>
-      <c r="W17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
-      <c r="X17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">425
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">1815
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -2878,107 +2911,109 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3686
-</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
+          <t xml:space="preserve">13680
+</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0821
+</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2861
+</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">463
+</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="N18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2248
+</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">973
+</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">321
 </t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">267
-</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">064
-</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">76
-</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">973
-</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321
-</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
+      <c r="R18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">252
 </t>
         </is>
       </c>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
+      <c r="S18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">664
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -2988,33 +3023,33 @@
 </t>
         </is>
       </c>
-      <c r="V18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">467
-</t>
-        </is>
-      </c>
-      <c r="W18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="W18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">712
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
@@ -3033,22 +3068,22 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>856</t>
+          <t xml:space="preserve">22606
+</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">263
 </t>
@@ -3060,9 +3095,9 @@
 </t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -3074,50 +3109,49 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-1254
+          <t xml:space="preserve">863
 </t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">1976
 </t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -3129,49 +3163,49 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">737
 </t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="V19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="X19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="X19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">711
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">783
 </t>
         </is>
       </c>
@@ -3200,21 +3234,21 @@
 </t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">415
-</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">245
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -3224,21 +3258,21 @@
 </t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -3250,13 +3284,13 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">662
-1254
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="N20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">354
 </t>
         </is>
       </c>
@@ -3268,30 +3302,31 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>304</t>
+          <t xml:space="preserve">04
+</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
-        </is>
-      </c>
-      <c r="R20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">301
+</t>
+        </is>
+      </c>
+      <c r="R20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">1623
 </t>
         </is>
       </c>
@@ -3303,31 +3338,31 @@
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="W20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">273
+</t>
+        </is>
+      </c>
+      <c r="W20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">7150
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -3358,19 +3393,19 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
@@ -3394,13 +3429,13 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -3412,19 +3447,19 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -3442,13 +3477,13 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">712
 </t>
         </is>
       </c>
@@ -3458,31 +3493,36 @@
 </t>
         </is>
       </c>
-      <c r="V21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">788
 </t>
         </is>
       </c>
       <c r="W21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">438
-</t>
-        </is>
-      </c>
-      <c r="X21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="3" t="n"/>
+          <t xml:space="preserve">773
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -3502,7 +3542,7 @@
 </t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">329
 </t>
@@ -3514,39 +3554,39 @@
 </t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -3558,19 +3598,19 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="N22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">975
 </t>
         </is>
       </c>
@@ -3594,47 +3634,52 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">893
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2126
-</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">1605
+</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="X22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="X22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="n"/>
+          <t xml:space="preserve">1860
+</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -3650,14 +3695,13 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7326
+          <t xml:space="preserve">174396
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">422999227
-1149 6
+          <t xml:space="preserve">1645
 </t>
         </is>
       </c>
@@ -3675,14 +3719,13 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">563
+          <t xml:space="preserve">2503
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4574532851
-12818
+          <t xml:space="preserve">11018
 </t>
         </is>
       </c>
@@ -3700,31 +3743,32 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1082
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1070
+          <t xml:space="preserve">11070
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">11268
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>489</t>
+          <t xml:space="preserve">14894
+</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -3735,7 +3779,7 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">557
+          <t xml:space="preserve">1557
 </t>
         </is>
       </c>
@@ -3747,50 +3791,49 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">893
+          <t xml:space="preserve">11468
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">3251
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">794
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">1344
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1203
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">1408
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">23990
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-78
+          <t xml:space="preserve">367
 </t>
         </is>
       </c>
@@ -3809,14 +3852,13 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">3479
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">575
-</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -3827,25 +3869,25 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">018
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -3855,12 +3897,7 @@
 </t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">216
@@ -3869,19 +3906,19 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="N24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">979
 </t>
         </is>
       </c>
@@ -3905,50 +3942,49 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
+          <t xml:space="preserve">1651
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">314
-</t>
-        </is>
-      </c>
-      <c r="W24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
-      <c r="X24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">408
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="W24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="X24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2822
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3990
+          <t xml:space="preserve">798
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-78
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -3967,19 +4003,20 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">067
-</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">315
+          <t xml:space="preserve">1067
+</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>206</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -3990,60 +4027,60 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24127
-210
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t xml:space="preserve">237
+</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>9861</t>
+          <t xml:space="preserve">221
+</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">779717
-1791818
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -4053,52 +4090,45 @@
 </t>
         </is>
       </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7783
-181186
+      <c r="R25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2841
+</t>
+        </is>
+      </c>
+      <c r="S25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6541
-</t>
-        </is>
-      </c>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1844
+</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="n"/>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="X25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="X25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">817
 </t>
         </is>
       </c>
@@ -4118,13 +4148,13 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">2900
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
@@ -4134,125 +4164,132 @@
 </t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1000
+</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">243
+</t>
+        </is>
+      </c>
+      <c r="R26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="S26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2809
+</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1920
+</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="X26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">791
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1918
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">24
 </t>
         </is>
       </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">080
-</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="T26" s="3" t="inlineStr">
-        <is>
-          <t>844</t>
-        </is>
-      </c>
-      <c r="U26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="W26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">872
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="3" t="n"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -4268,23 +4305,23 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
+          <t xml:space="preserve">23220
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">255
 </t>
@@ -4292,38 +4329,32 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">399
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-34
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="n"/>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -4341,7 +4372,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
@@ -4357,51 +4388,51 @@
 </t>
         </is>
       </c>
-      <c r="R27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
+      <c r="R27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="S27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">732
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="X27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
@@ -4421,13 +4452,14 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2907
+          <t xml:space="preserve">12907
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>205</t>
+          <t xml:space="preserve">518
+</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -4442,21 +4474,16 @@
 </t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">113
 </t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
+      <c r="H28" s="3" t="n"/>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -4468,11 +4495,11 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">209
 </t>
@@ -4484,7 +4511,7 @@
 </t>
         </is>
       </c>
-      <c r="N28" s="3" t="inlineStr">
+      <c r="N28" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">241
 </t>
@@ -4492,13 +4519,13 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">2973
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -4508,21 +4535,21 @@
 </t>
         </is>
       </c>
-      <c r="R28" s="3" t="inlineStr">
+      <c r="R28" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">248
 </t>
         </is>
       </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
+      <c r="S28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
+          <t xml:space="preserve">1602
 </t>
         </is>
       </c>
@@ -4532,32 +4559,33 @@
 </t>
         </is>
       </c>
-      <c r="V28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">246
+</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">726
 </t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -4576,42 +4604,38 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>865</t>
+          <t xml:space="preserve">121468
+</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">368
+          <t xml:space="preserve">315
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="n"/>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -4633,21 +4657,21 @@
 </t>
         </is>
       </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">506
+      <c r="M29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">953
 </t>
         </is>
       </c>
@@ -4663,57 +4687,57 @@
 </t>
         </is>
       </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">272
+      <c r="R29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="S29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="X29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="X29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -4732,49 +4756,49 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0566
+          <t xml:space="preserve">110562
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
+          <t xml:space="preserve">11452
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">11032
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4280
+          <t xml:space="preserve">1420
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">966
+          <t xml:space="preserve">1966
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
@@ -4786,13 +4810,13 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">11065
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1526
+          <t xml:space="preserve">11052
 </t>
         </is>
       </c>
@@ -4804,73 +4828,73 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
+          <t xml:space="preserve">4876
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">358
+          <t xml:space="preserve">111358
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">1201
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">11409
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">3968
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">11261
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">11159
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1359
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">14247
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -4895,7 +4919,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">452
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -4907,53 +4931,48 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
-        </is>
-      </c>
-      <c r="K31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11171
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">213
 </t>
         </is>
       </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
+      <c r="M31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">280
+</t>
+        </is>
+      </c>
+      <c r="N31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">248
 </t>
@@ -4961,73 +4980,73 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4826
+          <t xml:space="preserve">975
 </t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">972
-</t>
-        </is>
-      </c>
-      <c r="R31" s="3" t="inlineStr">
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
+      <c r="R31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">241
 </t>
         </is>
       </c>
-      <c r="S31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">409
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3968
-</t>
-        </is>
-      </c>
-      <c r="U31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">381
+          <t xml:space="preserve">794
+</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="V31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="X31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4417
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">1452
 </t>
         </is>
       </c>
@@ -5052,7 +5071,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
@@ -5064,17 +5083,17 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
@@ -5082,108 +5101,99 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="n"/>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11000
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">00
 </t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">785
-</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">439
+          <t xml:space="preserve">311
+</t>
+        </is>
+      </c>
+      <c r="R32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
-        </is>
-      </c>
-      <c r="U32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">1610
+</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">922
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="n"/>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1746
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -5202,34 +5212,35 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2423
+          <t xml:space="preserve">2133
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>2444</t>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
@@ -5237,7 +5248,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -5249,11 +5260,11 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="L33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">215
 </t>
@@ -5261,84 +5272,74 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="n"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600
+          <t xml:space="preserve">2990
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">289
+</t>
+        </is>
+      </c>
+      <c r="R33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2066
+</t>
+        </is>
+      </c>
+      <c r="S33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">709
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="V33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="W33" s="3" t="inlineStr">
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="W33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">238
 </t>
         </is>
       </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2862 2
-</t>
-        </is>
-      </c>
+      <c r="X33" s="3" t="n"/>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>8614</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -5363,18 +5364,17 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-214
-</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
+          <t xml:space="preserve">319
+</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">267
 </t>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -5406,11 +5406,11 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="L34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">218
 </t>
@@ -5424,19 +5424,19 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -5454,13 +5454,13 @@
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">1694
 </t>
         </is>
       </c>
@@ -5472,31 +5472,31 @@
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -5521,11 +5521,11 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
+          <t xml:space="preserve">311
+</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">208
 </t>
@@ -5551,19 +5551,19 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">060
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -5573,7 +5573,7 @@
 </t>
         </is>
       </c>
-      <c r="M35" s="3" t="inlineStr">
+      <c r="M35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">213
 </t>
@@ -5581,19 +5581,19 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">1972
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -5603,57 +5603,57 @@
 </t>
         </is>
       </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="S35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">302
+      <c r="R35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="S35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">16143
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
-      <c r="V35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">723
-</t>
-        </is>
-      </c>
-      <c r="W35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="X35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="W35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="X35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -5678,11 +5678,11 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
+          <t xml:space="preserve">321
+</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">209
 </t>
@@ -5696,13 +5696,13 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -5714,11 +5714,11 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="K36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">306
 </t>
@@ -5730,27 +5730,27 @@
 </t>
         </is>
       </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
+      <c r="M36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
+          <t xml:space="preserve">9185
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
@@ -5778,15 +5778,15 @@
 </t>
         </is>
       </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">820
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -5796,7 +5796,7 @@
 </t>
         </is>
       </c>
-      <c r="X36" s="3" t="inlineStr">
+      <c r="X36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">283
 </t>
@@ -5804,12 +5804,13 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>424</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">2110
+</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5827,19 +5828,19 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6937
+          <t xml:space="preserve">16937
 </t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">11554
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">11020
 </t>
         </is>
       </c>
@@ -5863,7 +5864,8 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">1101
+</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -5874,31 +5876,31 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
+          <t xml:space="preserve">1356
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">11060
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">18032
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1211
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">427
+          <t xml:space="preserve">4929
 </t>
         </is>
       </c>
@@ -5910,63 +5912,61 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">537
+          <t xml:space="preserve">1431
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">11262
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">792798
-11811
+          <t xml:space="preserve">11431
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3248
+          <t xml:space="preserve">138218
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">791
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">1368
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">466
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">11424
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7260
+          <t xml:space="preserve">3982
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82745857727
-12119
+          <t xml:space="preserve">13927
 </t>
         </is>
       </c>
@@ -5991,139 +5991,133 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="n"/>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">985
+</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="R38" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">252
 </t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">356
-</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">412
-</t>
-        </is>
-      </c>
-      <c r="M38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">410
-</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">985
-</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="Q38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">607
-</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="S38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">431
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">1690
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="V38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">368
-</t>
-        </is>
-      </c>
-      <c r="W38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="X38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">874
+</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">263
+</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">794
+          <t xml:space="preserve">789
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">397
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -6142,71 +6136,69 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>901</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
+          <t xml:space="preserve">3325
+</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">261
 </t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">17
 </t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>840</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-111
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="n"/>
+      <c r="L39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="M39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>206</t>
+          <t xml:space="preserve">246
+</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -6217,7 +6209,8 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">102
+</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -6226,57 +6219,57 @@
 </t>
         </is>
       </c>
-      <c r="R39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="S39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286
+      <c r="R39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1260
+</t>
+        </is>
+      </c>
+      <c r="S39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">632
+          <t xml:space="preserve">1632
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="V39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="V39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">2882
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -6295,14 +6288,13 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7924
-265
-</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">14531
+</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
@@ -6320,7 +6312,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -6332,7 +6324,7 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
@@ -6344,7 +6336,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -6354,88 +6346,87 @@
 </t>
         </is>
       </c>
-      <c r="M40" s="3" t="inlineStr">
+      <c r="M40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17978
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">328
+</t>
+        </is>
+      </c>
+      <c r="R40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">293
+</t>
+        </is>
+      </c>
+      <c r="T40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">392
+</t>
+        </is>
+      </c>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="W40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">269
-111
-</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">978
-</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">328
-</t>
-        </is>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="S40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="T40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="U40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="V40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="W40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="X40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -6454,14 +6445,13 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7924
-265
+          <t xml:space="preserve">2696
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
@@ -6471,9 +6461,9 @@
 </t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">856
 </t>
         </is>
       </c>
@@ -6485,7 +6475,7 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -6501,15 +6491,15 @@
 </t>
         </is>
       </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
+      <c r="K41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">436
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -6527,13 +6517,13 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -6551,48 +6541,49 @@
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">1928
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="V41" s="3" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="W41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="X41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="V41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8166
+</t>
+        </is>
+      </c>
+      <c r="W41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">834
+</t>
+        </is>
+      </c>
+      <c r="X41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">1905
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -6611,7 +6602,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2363
+          <t xml:space="preserve">12363
 </t>
         </is>
       </c>
@@ -6627,132 +6618,127 @@
 </t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="F42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">259
 </t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="N42" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">260
 </t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">412
-</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr">
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">241
 </t>
         </is>
       </c>
-      <c r="R42" s="3" t="inlineStr">
+      <c r="R42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">238
 </t>
         </is>
       </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
+      <c r="S42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">1977
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="W42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="W42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
-</t>
-        </is>
-      </c>
-      <c r="Z42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1906
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="n"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -6768,13 +6754,13 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
+          <t xml:space="preserve">3722
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
@@ -6786,7 +6772,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
@@ -6804,19 +6790,19 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -6828,18 +6814,19 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t xml:space="preserve">256
+</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
@@ -6857,55 +6844,55 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">804
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">756
+          <t xml:space="preserve">796
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="W43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="V43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">798
+</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">786
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -6930,7 +6917,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -6940,7 +6927,7 @@
 </t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="F44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">269
 </t>
@@ -6948,11 +6935,11 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">194
 </t>
@@ -6966,7 +6953,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -6984,11 +6971,11 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="N44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">269
 </t>
@@ -6996,13 +6983,13 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1060
+          <t xml:space="preserve">11000
 </t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -7014,23 +7001,23 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">621
-</t>
-        </is>
-      </c>
-      <c r="U44" s="3" t="inlineStr">
+          <t xml:space="preserve">1620
+</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
@@ -7038,31 +7025,31 @@
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">462
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="X44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">263
+</t>
+        </is>
+      </c>
+      <c r="X44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">841
+          <t xml:space="preserve">844
 </t>
         </is>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">1660
 </t>
         </is>
       </c>
@@ -7079,135 +7066,119 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">326
-</t>
-        </is>
-      </c>
+      <c r="C45" s="3" t="n"/>
+      <c r="D45" s="3" t="n"/>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">021
+          <t xml:space="preserve">11210
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">561
+          <t xml:space="preserve">17961
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">1091
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1147
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7283
+          <t xml:space="preserve">1723
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7263
+          <t xml:space="preserve">116 69
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">987
+          <t xml:space="preserve">1487
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
+          <t xml:space="preserve">2938
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="n"/>
+          <t xml:space="preserve">17528
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1491
+</t>
+        </is>
+      </c>
       <c r="S45" s="3" t="n"/>
-      <c r="T45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4500
-</t>
-        </is>
-      </c>
+      <c r="T45" s="3" t="n"/>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
+          <t xml:space="preserve">1686
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3581
-</t>
-        </is>
-      </c>
-      <c r="W45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="X45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1725
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1381
+</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="n"/>
+      <c r="X45" s="3" t="n"/>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="n"/>
+          <t xml:space="preserve">35037
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93160
+</t>
+        </is>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -7223,31 +7194,31 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">376
+          <t xml:space="preserve">23376
 </t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
+          <t xml:space="preserve">311
+</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">260
 </t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -7265,23 +7236,18 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">283
-</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">411
-</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
+          <t xml:space="preserve">531
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="n"/>
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="M46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">200
 </t>
@@ -7301,7 +7267,7 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -7311,13 +7277,13 @@
 </t>
         </is>
       </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
+      <c r="R46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2168
+</t>
+        </is>
+      </c>
+      <c r="S46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">290
 </t>
@@ -7325,41 +7291,45 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">7290
 </t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63
-</t>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
+          <t>6434</t>
         </is>
       </c>
       <c r="W46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="3" t="n"/>
+          <t xml:space="preserve">2839
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1862
+          <t xml:space="preserve">1362
 </t>
         </is>
       </c>
@@ -755,30 +755,31 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t xml:space="preserve">245
+</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">817
+</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -788,7 +789,7 @@
 </t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">202
 </t>
@@ -800,34 +801,39 @@
 </t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">834
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="n"/>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">241
 </t>
         </is>
       </c>
-      <c r="S4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">271
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -837,7 +843,7 @@
 </t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">122
 </t>
@@ -851,11 +857,11 @@
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="X4" s="8" t="inlineStr">
+          <t xml:space="preserve">828
+</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">262
 </t>
@@ -863,13 +869,13 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18118
+          <t xml:space="preserve">1818
 </t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -888,7 +894,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29038
+          <t xml:space="preserve">2038
 </t>
         </is>
       </c>
@@ -912,7 +918,8 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">144
+</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -935,11 +942,11 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L5" s="8" t="inlineStr">
+          <t xml:space="preserve">010
+</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
@@ -951,7 +958,7 @@
 </t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">216
 </t>
@@ -959,13 +966,13 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">9090
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -975,7 +982,7 @@
 </t>
         </is>
       </c>
-      <c r="R5" s="8" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">254
 </t>
@@ -989,7 +996,7 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1566
+          <t xml:space="preserve">566
 </t>
         </is>
       </c>
@@ -999,13 +1006,13 @@
 </t>
         </is>
       </c>
-      <c r="V5" s="8" t="inlineStr">
+      <c r="V5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">272
 </t>
         </is>
       </c>
-      <c r="W5" s="8" t="inlineStr">
+      <c r="W5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">240
 </t>
@@ -1013,19 +1020,20 @@
       </c>
       <c r="X5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">728
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">1411
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t xml:space="preserve">82
+</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1043,11 +1051,11 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14223
-</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
+          <t xml:space="preserve">1223
+</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">342
 </t>
@@ -1055,7 +1063,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1073,7 +1081,7 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8726
+          <t xml:space="preserve">1846
 </t>
         </is>
       </c>
@@ -1091,7 +1099,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1119,15 +1127,15 @@
 </t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
@@ -1137,7 +1145,7 @@
 </t>
         </is>
       </c>
-      <c r="S6" s="8" t="inlineStr">
+      <c r="S6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">286
 </t>
@@ -1145,13 +1153,13 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29298
-</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -1161,9 +1169,9 @@
 </t>
         </is>
       </c>
-      <c r="W6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">237
+      <c r="W6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
@@ -1175,13 +1183,14 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664
+          <t xml:space="preserve">166141
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t>138</t>
+          <t xml:space="preserve">132
+</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1199,23 +1208,25 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>47851</t>
+          <t xml:space="preserve">64725
+</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">347
+</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -1233,18 +1244,19 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">479
+</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1274,23 +1286,23 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="Q7" s="8" t="inlineStr">
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">342
 </t>
         </is>
       </c>
-      <c r="R7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="S7" s="8" t="inlineStr">
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">271
 </t>
@@ -1298,11 +1310,11 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
-</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">265
 </t>
@@ -1314,7 +1326,7 @@
 </t>
         </is>
       </c>
-      <c r="W7" s="8" t="inlineStr">
+      <c r="W7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">244
 </t>
@@ -1328,13 +1340,13 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1662
+          <t xml:space="preserve">662
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -1353,17 +1365,17 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12990
-</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
+          <t xml:space="preserve">2990
+</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">346
 </t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">206
 </t>
@@ -1383,23 +1395,23 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">309
 </t>
@@ -1411,7 +1423,7 @@
 </t>
         </is>
       </c>
-      <c r="M8" s="8" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">206
 </t>
@@ -1425,17 +1437,17 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1965
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="inlineStr">
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">214
 </t>
@@ -1449,19 +1461,19 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -1471,9 +1483,9 @@
 </t>
         </is>
       </c>
-      <c r="W8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">019
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -1485,7 +1497,7 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
+          <t xml:space="preserve">914
 </t>
         </is>
       </c>
@@ -1510,7 +1522,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117835
+          <t xml:space="preserve">17812
 </t>
         </is>
       </c>
@@ -1522,19 +1534,19 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1969
+          <t xml:space="preserve">969
 </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11308
+          <t xml:space="preserve">130 17
 </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1619
+          <t xml:space="preserve">659
 </t>
         </is>
       </c>
@@ -1546,13 +1558,13 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1275
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -1570,7 +1582,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1996
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
@@ -1582,31 +1594,31 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14945
+          <t xml:space="preserve">8942
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1496
+          <t xml:space="preserve">11796
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11357
+          <t xml:space="preserve">1551
 </t>
         </is>
       </c>
@@ -1618,7 +1630,7 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0960
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -1636,13 +1648,13 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11335
+          <t xml:space="preserve">1335
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13888
+          <t xml:space="preserve">3888
 </t>
         </is>
       </c>
@@ -1667,13 +1679,13 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3567
-</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3930
+          <t xml:space="preserve">81885
+</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">330
 </t>
         </is>
       </c>
@@ -1689,7 +1701,7 @@
 </t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">136
 </t>
@@ -1697,7 +1709,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -1709,12 +1721,12 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="K10" s="3" t="n"/>
-      <c r="L10" s="8" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">200
 </t>
@@ -1744,27 +1756,27 @@
 </t>
         </is>
       </c>
-      <c r="Q10" s="8" t="inlineStr">
+      <c r="Q10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">299
 </t>
         </is>
       </c>
-      <c r="R10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">944
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1660
+          <t xml:space="preserve">660
 </t>
         </is>
       </c>
@@ -1780,27 +1792,27 @@
 </t>
         </is>
       </c>
-      <c r="W10" s="8" t="inlineStr">
+      <c r="W10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">234
 </t>
         </is>
       </c>
-      <c r="X10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">267
+      <c r="X10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
+          <t xml:space="preserve">728
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -1823,7 +1835,7 @@
 </t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">301
 </t>
@@ -1855,7 +1867,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1867,7 +1879,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1877,15 +1889,15 @@
 </t>
         </is>
       </c>
-      <c r="M11" s="8" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">209
 </t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">245
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -1897,7 +1909,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -1913,7 +1925,7 @@
 </t>
         </is>
       </c>
-      <c r="S11" s="3" t="inlineStr">
+      <c r="S11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">298
 </t>
@@ -1921,7 +1933,7 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1706
+          <t xml:space="preserve">7206
 </t>
         </is>
       </c>
@@ -1933,13 +1945,13 @@
       </c>
       <c r="V11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">721
+</t>
+        </is>
+      </c>
+      <c r="W11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -1951,13 +1963,13 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840
+          <t xml:space="preserve">28940
 </t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -1976,19 +1988,19 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2471
-</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">818
-</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">3471
+</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">918
+</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
@@ -2004,15 +2016,15 @@
 </t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">212
 </t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2271
 </t>
         </is>
       </c>
@@ -2024,11 +2036,11 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">233
 </t>
@@ -2036,67 +2048,66 @@
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
+          <t>3505</t>
+        </is>
+      </c>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">974
+</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">318
+</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">518
+</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">219
 </t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">275
-</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">318
-</t>
-        </is>
-      </c>
-      <c r="R12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="S12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">271
-</t>
-        </is>
-      </c>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">598
-</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="W12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2846
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -2114,7 +2125,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -2133,11 +2144,11 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14286
-</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
+          <t xml:space="preserve">4286
+</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">328
 </t>
@@ -2145,13 +2156,13 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">866
 </t>
         </is>
       </c>
@@ -2169,19 +2180,19 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2221,21 +2232,21 @@
 </t>
         </is>
       </c>
-      <c r="R13" s="8" t="inlineStr">
+      <c r="R13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">246
 </t>
         </is>
       </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
+      <c r="S13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">527
+          <t xml:space="preserve">4274
 </t>
         </is>
       </c>
@@ -2245,7 +2256,7 @@
 </t>
         </is>
       </c>
-      <c r="V13" s="8" t="inlineStr">
+      <c r="V13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">280
 </t>
@@ -2259,7 +2270,7 @@
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
@@ -2271,7 +2282,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -2296,7 +2307,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
@@ -2318,7 +2329,7 @@
 </t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">203
 </t>
@@ -2336,12 +2347,7 @@
 </t>
         </is>
       </c>
-      <c r="K14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
+      <c r="K14" s="3" t="n"/>
       <c r="L14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">224
@@ -2356,24 +2362,25 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t xml:space="preserve">264
+</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1973
+          <t xml:space="preserve">973
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">824
 </t>
         </is>
       </c>
@@ -2383,7 +2390,7 @@
 </t>
         </is>
       </c>
-      <c r="S14" s="8" t="inlineStr">
+      <c r="S14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">242
 </t>
@@ -2391,7 +2398,7 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -2407,13 +2414,13 @@
 </t>
         </is>
       </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="X14" s="8" t="inlineStr">
+      <c r="W14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2116
+</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">255
 </t>
@@ -2421,13 +2428,14 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t>091</t>
+          <t xml:space="preserve">109
+</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2445,7 +2453,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3596
+          <t xml:space="preserve">2828
 </t>
         </is>
       </c>
@@ -2455,13 +2463,13 @@
 </t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">208
 </t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">267
 </t>
@@ -2481,7 +2489,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -2491,9 +2499,9 @@
 </t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">517
 </t>
         </is>
       </c>
@@ -2503,7 +2511,7 @@
 </t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="M15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">216
 </t>
@@ -2517,17 +2525,17 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="Q15" s="8" t="inlineStr">
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">320
 </t>
@@ -2547,7 +2555,7 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1617
+          <t xml:space="preserve">617
 </t>
         </is>
       </c>
@@ -2563,7 +2571,7 @@
 </t>
         </is>
       </c>
-      <c r="W15" s="8" t="inlineStr">
+      <c r="W15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">248
 </t>
@@ -2577,13 +2585,13 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">731
+          <t xml:space="preserve">7381
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1006
 </t>
         </is>
       </c>
@@ -2608,19 +2616,19 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1579
+          <t xml:space="preserve">1679
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11055
+          <t xml:space="preserve">1055
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51317
+          <t xml:space="preserve">1514
 </t>
         </is>
       </c>
@@ -2638,7 +2646,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -2668,13 +2676,13 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11307
+          <t xml:space="preserve">12307
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274901
+          <t xml:space="preserve">24901
 </t>
         </is>
       </c>
@@ -2692,13 +2700,13 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11219
+          <t xml:space="preserve">1219
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11361
+          <t xml:space="preserve">11362
 </t>
         </is>
       </c>
@@ -2710,7 +2718,7 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1766
+          <t xml:space="preserve">766
 </t>
         </is>
       </c>
@@ -2722,19 +2730,19 @@
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11207
+          <t xml:space="preserve">1207
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1625
+          <t xml:space="preserve">1425
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14074
+          <t xml:space="preserve">14076
 </t>
         </is>
       </c>
@@ -2759,13 +2767,13 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13182
+          <t xml:space="preserve">3182
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">816
 </t>
         </is>
       </c>
@@ -2805,14 +2813,19 @@
 </t>
         </is>
       </c>
-      <c r="K17" s="3" t="n"/>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">221
 </t>
         </is>
       </c>
-      <c r="M17" s="8" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">219
 </t>
@@ -2826,7 +2839,7 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">3980
 </t>
         </is>
       </c>
@@ -2838,7 +2851,7 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
@@ -2848,45 +2861,44 @@
 </t>
         </is>
       </c>
-      <c r="S17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664
+          <t xml:space="preserve">664
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">267
-</t>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>063</t>
         </is>
       </c>
       <c r="W17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
-      <c r="X17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="X17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">846
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1815
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
@@ -2911,25 +2923,25 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13680
-</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0821
+          <t xml:space="preserve">3680
+</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2861
+          <t xml:space="preserve">861
 </t>
         </is>
       </c>
@@ -2941,7 +2953,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">804
 </t>
         </is>
       </c>
@@ -2951,15 +2963,15 @@
 </t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">463
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">064
 </t>
         </is>
       </c>
@@ -2977,13 +2989,13 @@
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2248
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">973
+          <t xml:space="preserve">913
 </t>
         </is>
       </c>
@@ -3005,7 +3017,7 @@
 </t>
         </is>
       </c>
-      <c r="S18" s="8" t="inlineStr">
+      <c r="S18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">277
 </t>
@@ -3013,7 +3025,7 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -3023,13 +3035,13 @@
 </t>
         </is>
       </c>
-      <c r="V18" s="8" t="inlineStr">
+      <c r="V18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">285
 </t>
         </is>
       </c>
-      <c r="W18" s="8" t="inlineStr">
+      <c r="W18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">244
 </t>
@@ -3043,7 +3055,7 @@
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">712
+          <t xml:space="preserve">714
 </t>
         </is>
       </c>
@@ -3068,13 +3080,14 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22606
+          <t xml:space="preserve">2656
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t xml:space="preserve">304
+</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -3083,7 +3096,7 @@
 </t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">263
 </t>
@@ -3095,7 +3108,7 @@
 </t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">214
 </t>
@@ -3109,17 +3122,17 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="L19" s="8" t="inlineStr">
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">223
 </t>
@@ -3133,23 +3146,23 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1976
+          <t xml:space="preserve">976
 </t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
+          <t xml:space="preserve">806
+</t>
+        </is>
+      </c>
+      <c r="Q19" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">299
 </t>
@@ -3163,7 +3176,7 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">511
 </t>
         </is>
       </c>
@@ -3181,31 +3194,31 @@
       </c>
       <c r="V19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
-        </is>
-      </c>
-      <c r="W19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="X19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">711
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
+      <c r="W19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2898
+</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">8290
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">783
+          <t xml:space="preserve">1859
 </t>
         </is>
       </c>
@@ -3224,7 +3237,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3659
+          <t xml:space="preserve">38659
 </t>
         </is>
       </c>
@@ -3242,7 +3255,7 @@
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">081
 </t>
         </is>
       </c>
@@ -3258,9 +3271,9 @@
 </t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -3288,15 +3301,15 @@
 </t>
         </is>
       </c>
-      <c r="N20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">354
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">9280
 </t>
         </is>
       </c>
@@ -3308,11 +3321,11 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
-        </is>
-      </c>
-      <c r="R20" s="8" t="inlineStr">
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">248
 </t>
@@ -3326,7 +3339,7 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1623
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -3344,19 +3357,19 @@
       </c>
       <c r="W20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7150
+          <t xml:space="preserve">1250
 </t>
         </is>
       </c>
@@ -3405,7 +3418,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -3429,37 +3442,37 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -3477,7 +3490,7 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -3493,15 +3506,15 @@
 </t>
         </is>
       </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">788
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="W21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">466
 </t>
         </is>
       </c>
@@ -3513,13 +3526,13 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">773
+          <t xml:space="preserve">7123
 </t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -3542,7 +3555,7 @@
 </t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">329
 </t>
@@ -3554,7 +3567,7 @@
 </t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">270
 </t>
@@ -3574,19 +3587,19 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -3598,11 +3611,11 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="N22" s="8" t="inlineStr">
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">247
 </t>
@@ -3640,19 +3653,19 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
+          <t xml:space="preserve">605
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">865
 </t>
         </is>
       </c>
@@ -3664,19 +3677,19 @@
       </c>
       <c r="X22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1860
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">12449
 </t>
         </is>
       </c>
@@ -3695,19 +3708,18 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174396
-</t>
+          <t>85196</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645
+          <t xml:space="preserve">14685
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
+          <t xml:space="preserve">10742
 </t>
         </is>
       </c>
@@ -3719,13 +3731,13 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2503
+          <t xml:space="preserve">503
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11018
+          <t xml:space="preserve">1018
 </t>
         </is>
       </c>
@@ -3737,14 +3749,12 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -3761,13 +3771,13 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11268
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14894
+          <t xml:space="preserve">4894
 </t>
         </is>
       </c>
@@ -3779,7 +3789,7 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1557
+          <t xml:space="preserve">15657
 </t>
         </is>
       </c>
@@ -3791,13 +3801,13 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11468
+          <t xml:space="preserve">1468
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3251
+          <t xml:space="preserve">33251
 </t>
         </is>
       </c>
@@ -3809,7 +3819,7 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1344
+          <t xml:space="preserve">1384
 </t>
         </is>
       </c>
@@ -3827,13 +3837,13 @@
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23990
+          <t xml:space="preserve">3990
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">367
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
@@ -3852,13 +3862,13 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3479
-</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t xml:space="preserve">315
+</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -3897,7 +3907,12 @@
 </t>
         </is>
       </c>
-      <c r="K24" s="3" t="n"/>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">216
@@ -3910,9 +3925,9 @@
 </t>
         </is>
       </c>
-      <c r="N24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -3924,7 +3939,7 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -3942,13 +3957,13 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1651
+          <t xml:space="preserve">651
 </t>
         </is>
       </c>
@@ -3964,7 +3979,7 @@
 </t>
         </is>
       </c>
-      <c r="W24" s="8" t="inlineStr">
+      <c r="W24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">241
 </t>
@@ -3972,7 +3987,7 @@
       </c>
       <c r="X24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2822
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -3984,7 +3999,7 @@
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -4007,7 +4022,7 @@
 </t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">263
 </t>
@@ -4021,13 +4036,13 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -4051,7 +4066,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
@@ -4069,18 +4084,19 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t xml:space="preserve">264
+</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">9140
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -4090,13 +4106,13 @@
 </t>
         </is>
       </c>
-      <c r="R25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2841
-</t>
-        </is>
-      </c>
-      <c r="S25" s="8" t="inlineStr">
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">841
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">287
 </t>
@@ -4104,16 +4120,17 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1844
-</t>
-        </is>
-      </c>
-      <c r="U25" s="3" t="n"/>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t>2441</t>
-        </is>
-      </c>
+          <t xml:space="preserve">844
+</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="n"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">228
@@ -4128,7 +4145,7 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">817
+          <t xml:space="preserve">84174
 </t>
         </is>
       </c>
@@ -4160,19 +4177,19 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -4184,19 +4201,19 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">041
 </t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
@@ -4214,7 +4231,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -4226,7 +4243,7 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4236,27 +4253,27 @@
 </t>
         </is>
       </c>
-      <c r="R26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="S26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2809
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -4274,19 +4291,19 @@
       </c>
       <c r="X26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">791
+          <t xml:space="preserve">711
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1918
+          <t xml:space="preserve">0918
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
@@ -4305,65 +4322,68 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23220
+          <t xml:space="preserve">3220
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">854
+</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">205
 </t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
-      </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">240
@@ -4372,7 +4392,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -4390,19 +4410,19 @@
       </c>
       <c r="R27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="S27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -4414,19 +4434,19 @@
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">869
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">944
 </t>
         </is>
       </c>
       <c r="X27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">2890
 </t>
         </is>
       </c>
@@ -4436,7 +4456,12 @@
 </t>
         </is>
       </c>
-      <c r="Z27" s="3" t="n"/>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -4452,13 +4477,13 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12907
-</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">518
+          <t xml:space="preserve">2907
+</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
@@ -4480,7 +4505,12 @@
 </t>
         </is>
       </c>
-      <c r="H28" s="3" t="n"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">22
@@ -4495,11 +4525,11 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">209
 </t>
@@ -4511,7 +4541,7 @@
 </t>
         </is>
       </c>
-      <c r="N28" s="8" t="inlineStr">
+      <c r="N28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">241
 </t>
@@ -4519,13 +4549,13 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2973
+          <t xml:space="preserve">973
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -4535,13 +4565,13 @@
 </t>
         </is>
       </c>
-      <c r="R28" s="8" t="inlineStr">
+      <c r="R28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">248
 </t>
         </is>
       </c>
-      <c r="S28" s="8" t="inlineStr">
+      <c r="S28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">272
 </t>
@@ -4549,7 +4579,7 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1602
+          <t xml:space="preserve">602
 </t>
         </is>
       </c>
@@ -4559,7 +4589,7 @@
 </t>
         </is>
       </c>
-      <c r="V28" s="8" t="inlineStr">
+      <c r="V28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">286
 </t>
@@ -4585,7 +4615,7 @@
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">1074
 </t>
         </is>
       </c>
@@ -4604,13 +4634,13 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121468
-</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">315
+          <t xml:space="preserve">2468
+</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -4622,26 +4652,31 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="n"/>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -4657,7 +4692,7 @@
 </t>
         </is>
       </c>
-      <c r="M29" s="8" t="inlineStr">
+      <c r="M29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">206
 </t>
@@ -4683,17 +4718,17 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">853
-</t>
-        </is>
-      </c>
-      <c r="R29" s="8" t="inlineStr">
+          <t xml:space="preserve">859
+</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">236
 </t>
         </is>
       </c>
-      <c r="S29" s="8" t="inlineStr">
+      <c r="S29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">280
 </t>
@@ -4701,7 +4736,7 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">8210
 </t>
         </is>
       </c>
@@ -4725,7 +4760,7 @@
       </c>
       <c r="X29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -4737,7 +4772,7 @@
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4768,19 +4803,19 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11032
+          <t xml:space="preserve">1032
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">11242
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1420
+          <t xml:space="preserve">420
 </t>
         </is>
       </c>
@@ -4804,25 +4839,25 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">388
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11065
+          <t xml:space="preserve">1065
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11052
+          <t xml:space="preserve">1052
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
@@ -4834,13 +4869,13 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111358
+          <t xml:space="preserve">11358
 </t>
         </is>
       </c>
@@ -4852,7 +4887,7 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11409
+          <t xml:space="preserve">1409
 </t>
         </is>
       </c>
@@ -4864,7 +4899,7 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -4876,13 +4911,13 @@
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11159
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1359
+          <t xml:space="preserve">1329
 </t>
         </is>
       </c>
@@ -4894,7 +4929,7 @@
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -4919,65 +4954,69 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">086
+</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 0
+</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">248
 </t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="M31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
-      <c r="N31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">975
@@ -4986,7 +5025,7 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -4996,7 +5035,7 @@
 </t>
         </is>
       </c>
-      <c r="R31" s="8" t="inlineStr">
+      <c r="R31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">241
 </t>
@@ -5014,13 +5053,13 @@
 </t>
         </is>
       </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">888
-</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">252
 </t>
@@ -5034,7 +5073,7 @@
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">972
 </t>
         </is>
       </c>
@@ -5046,7 +5085,7 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1452
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
@@ -5065,7 +5104,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3847
+          <t xml:space="preserve">88169
 </t>
         </is>
       </c>
@@ -5101,19 +5140,19 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5129,10 +5168,15 @@
 </t>
         </is>
       </c>
-      <c r="N32" s="3" t="n"/>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
@@ -5148,27 +5192,27 @@
 </t>
         </is>
       </c>
-      <c r="R32" s="8" t="inlineStr">
+      <c r="R32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">249
 </t>
         </is>
       </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">275
+      <c r="S32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">725
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1610
-</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">610
+</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -5184,10 +5228,15 @@
 </t>
         </is>
       </c>
-      <c r="X32" s="3" t="n"/>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">972
+</t>
+        </is>
+      </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1746
+          <t xml:space="preserve">761
 </t>
         </is>
       </c>
@@ -5228,7 +5277,7 @@
 </t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">244
 </t>
@@ -5236,11 +5285,11 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="inlineStr">
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
@@ -5248,7 +5297,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -5260,13 +5309,13 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="L33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
@@ -5276,32 +5325,37 @@
 </t>
         </is>
       </c>
-      <c r="N33" s="3" t="n"/>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
-        </is>
-      </c>
-      <c r="R33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2066
-</t>
-        </is>
-      </c>
-      <c r="S33" s="8" t="inlineStr">
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">282
 </t>
@@ -5309,17 +5363,17 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">709
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">256
 </t>
@@ -5331,15 +5385,21 @@
 </t>
         </is>
       </c>
-      <c r="X33" s="3" t="n"/>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">283
+</t>
+        </is>
+      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t xml:space="preserve">862
+</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -5362,15 +5422,15 @@
 </t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">319
 </t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -5382,7 +5442,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -5400,7 +5460,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">395
 </t>
         </is>
       </c>
@@ -5410,7 +5470,7 @@
 </t>
         </is>
       </c>
-      <c r="L34" s="8" t="inlineStr">
+      <c r="L34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">218
 </t>
@@ -5430,25 +5490,25 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -5460,7 +5520,7 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1694
+          <t xml:space="preserve">694
 </t>
         </is>
       </c>
@@ -5490,7 +5550,7 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
@@ -5525,13 +5585,13 @@
 </t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">208
 </t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">259
 </t>
@@ -5557,13 +5617,13 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5573,7 +5633,7 @@
 </t>
         </is>
       </c>
-      <c r="M35" s="8" t="inlineStr">
+      <c r="M35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">213
 </t>
@@ -5587,13 +5647,13 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1972
+          <t xml:space="preserve">972
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">071
 </t>
         </is>
       </c>
@@ -5603,13 +5663,13 @@
 </t>
         </is>
       </c>
-      <c r="R35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="S35" s="8" t="inlineStr">
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">278
 </t>
@@ -5617,7 +5677,7 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16143
+          <t xml:space="preserve">613
 </t>
         </is>
       </c>
@@ -5627,7 +5687,7 @@
 </t>
         </is>
       </c>
-      <c r="V35" s="8" t="inlineStr">
+      <c r="V35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">218
 </t>
@@ -5639,7 +5699,7 @@
 </t>
         </is>
       </c>
-      <c r="X35" s="8" t="inlineStr">
+      <c r="X35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">289
 </t>
@@ -5647,13 +5707,13 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">779
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">8111
 </t>
         </is>
       </c>
@@ -5682,7 +5742,7 @@
 </t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">209
 </t>
@@ -5694,7 +5754,7 @@
 </t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="G36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">112
 </t>
@@ -5714,11 +5774,11 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="K36" s="8" t="inlineStr">
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">306
 </t>
@@ -5730,27 +5790,27 @@
 </t>
         </is>
       </c>
-      <c r="M36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9185
+          <t xml:space="preserve">985
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -5798,18 +5858,19 @@
       </c>
       <c r="X36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>424</t>
+          <t xml:space="preserve">1720
+</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2110
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -5834,13 +5895,13 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11554
+          <t xml:space="preserve">1554
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11020
+          <t xml:space="preserve">1020
 </t>
         </is>
       </c>
@@ -5876,7 +5937,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1356
+          <t xml:space="preserve">356
 </t>
         </is>
       </c>
@@ -5888,61 +5949,61 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18032
+          <t xml:space="preserve">1052
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1211
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4929
+          <t xml:space="preserve">4927
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">17 1
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1531
+</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1262
+</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1431
 </t>
         </is>
       </c>
-      <c r="R37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11262
-</t>
-        </is>
-      </c>
-      <c r="S37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11431
-</t>
-        </is>
-      </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138218
+          <t xml:space="preserve">82168
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">791
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1368
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
@@ -5954,7 +6015,7 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11424
+          <t xml:space="preserve">1024
 </t>
         </is>
       </c>
@@ -5966,7 +6027,7 @@
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13927
+          <t xml:space="preserve">8921
 </t>
         </is>
       </c>
@@ -5997,7 +6058,8 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>204</t>
+          <t xml:space="preserve">204
+</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -6014,13 +6076,13 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -6057,13 +6119,13 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
@@ -6081,17 +6143,17 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">874
 </t>
@@ -6099,25 +6161,25 @@
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">789
+          <t xml:space="preserve">780
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">5661
 </t>
         </is>
       </c>
@@ -6136,96 +6198,101 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3325
+          <t xml:space="preserve">32325
 </t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">82181
+</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">119
 </t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="H39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="n"/>
-      <c r="L39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="M39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="Q39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">319
-</t>
-        </is>
-      </c>
       <c r="R39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
-</t>
-        </is>
-      </c>
-      <c r="S39" s="8" t="inlineStr">
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">298
 </t>
@@ -6239,37 +6306,37 @@
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="V39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">491
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2882
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -6288,13 +6355,13 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14531
+          <t xml:space="preserve">15341
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
@@ -6324,19 +6391,19 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6346,7 +6413,7 @@
 </t>
         </is>
       </c>
-      <c r="M40" s="8" t="inlineStr">
+      <c r="M40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">196
 </t>
@@ -6354,19 +6421,19 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17978
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
@@ -6376,7 +6443,7 @@
 </t>
         </is>
       </c>
-      <c r="R40" s="8" t="inlineStr">
+      <c r="R40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">260
 </t>
@@ -6402,7 +6469,7 @@
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -6420,13 +6487,13 @@
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">1016
 </t>
         </is>
       </c>
@@ -6445,7 +6512,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2696
+          <t xml:space="preserve">9656
 </t>
         </is>
       </c>
@@ -6463,7 +6530,7 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
@@ -6491,10 +6558,9 @@
 </t>
         </is>
       </c>
-      <c r="K41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">436
-</t>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>46</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
@@ -6517,13 +6583,13 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -6547,43 +6613,43 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="V41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8166
-</t>
-        </is>
-      </c>
-      <c r="W41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">834
+          <t xml:space="preserve">466
+</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="X41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">92180
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1905
+          <t xml:space="preserve">905
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -6602,7 +6668,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12363
+          <t xml:space="preserve">8363
 </t>
         </is>
       </c>
@@ -6612,13 +6678,13 @@
 </t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">039
+</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">259
 </t>
@@ -6638,17 +6704,17 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr">
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">281
 </t>
@@ -6666,15 +6732,15 @@
 </t>
         </is>
       </c>
-      <c r="N42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">18990
 </t>
         </is>
       </c>
@@ -6684,19 +6750,19 @@
 </t>
         </is>
       </c>
-      <c r="Q42" s="8" t="inlineStr">
+      <c r="Q42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">241
 </t>
         </is>
       </c>
-      <c r="R42" s="8" t="inlineStr">
+      <c r="R42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">238
 </t>
         </is>
       </c>
-      <c r="S42" s="8" t="inlineStr">
+      <c r="S42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">293
 </t>
@@ -6704,41 +6770,46 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1977
+          <t xml:space="preserve">977
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="V42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="V42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8229
 </t>
         </is>
       </c>
       <c r="W42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
-        </is>
-      </c>
-      <c r="X42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">825
+</t>
+        </is>
+      </c>
+      <c r="X42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1906
-</t>
-        </is>
-      </c>
-      <c r="Z42" s="3" t="n"/>
+          <t xml:space="preserve">906
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -6772,7 +6843,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
@@ -6790,19 +6861,19 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6826,7 +6897,7 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -6844,7 +6915,7 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
@@ -6856,25 +6927,25 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">796
+          <t xml:space="preserve">756
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">798
-</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="W43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">414
 </t>
         </is>
       </c>
@@ -6892,7 +6963,7 @@
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1982
 </t>
         </is>
       </c>
@@ -6911,7 +6982,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3659
+          <t xml:space="preserve">659
 </t>
         </is>
       </c>
@@ -6927,7 +6998,7 @@
 </t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">269
 </t>
@@ -6939,9 +7010,9 @@
 </t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
@@ -6953,7 +7024,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -6965,7 +7036,7 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -6975,7 +7046,7 @@
 </t>
         </is>
       </c>
-      <c r="N44" s="8" t="inlineStr">
+      <c r="N44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">269
 </t>
@@ -6983,13 +7054,13 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -6999,7 +7070,7 @@
 </t>
         </is>
       </c>
-      <c r="R44" s="3" t="inlineStr">
+      <c r="R44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">264
 </t>
@@ -7007,7 +7078,7 @@
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">806
 </t>
         </is>
       </c>
@@ -7017,9 +7088,9 @@
 </t>
         </is>
       </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">086
 </t>
         </is>
       </c>
@@ -7035,9 +7106,9 @@
 </t>
         </is>
       </c>
-      <c r="X44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">322
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
@@ -7049,7 +7120,7 @@
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1660
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -7066,116 +7137,145 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="n"/>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20262
+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191656
+</t>
+        </is>
+      </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11210
+          <t xml:space="preserve">11280
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17961
+          <t xml:space="preserve">20261
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1091
+          <t xml:space="preserve">091
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
+          <t xml:space="preserve">11142
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>107</t>
+          <t xml:space="preserve">11010
+</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1723
-</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116 69
+          <t xml:space="preserve">116659
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1487
+          <t xml:space="preserve">11488
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2938
+          <t xml:space="preserve">2928
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17528
+          <t xml:space="preserve">1728
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1491
-</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="n"/>
-      <c r="T45" s="3" t="n"/>
+          <t xml:space="preserve">014691
+</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1741
+</t>
+        </is>
+      </c>
+      <c r="T45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14508
+</t>
+        </is>
+      </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1686
+          <t xml:space="preserve">656
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1381
-</t>
-        </is>
-      </c>
-      <c r="W45" s="3" t="n"/>
-      <c r="X45" s="3" t="n"/>
+          <t xml:space="preserve">1581
+</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1722
+</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35037
+          <t xml:space="preserve">9001
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93160
+          <t xml:space="preserve">560
 </t>
         </is>
       </c>
@@ -7194,23 +7294,23 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23376
-</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311
-</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
+          <t xml:space="preserve">2376
+</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">317
+</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">202
 </t>
         </is>
       </c>
-      <c r="F46" s="8" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">260
 </t>
@@ -7218,7 +7318,7 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -7236,18 +7336,23 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">531
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n"/>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="L46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">111
 </t>
         </is>
       </c>
-      <c r="M46" s="8" t="inlineStr">
+      <c r="M46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">200
 </t>
@@ -7267,7 +7372,7 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -7277,13 +7382,13 @@
 </t>
         </is>
       </c>
-      <c r="R46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2168
-</t>
-        </is>
-      </c>
-      <c r="S46" s="8" t="inlineStr">
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">290
 </t>
@@ -7291,7 +7396,7 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7290
+          <t xml:space="preserve">729
 </t>
         </is>
       </c>
@@ -7301,12 +7406,13 @@
 </t>
         </is>
       </c>
-      <c r="V46" s="8" t="inlineStr">
-        <is>
-          <t>6434</t>
-        </is>
-      </c>
-      <c r="W46" s="8" t="inlineStr">
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">263
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">241
 </t>
@@ -7314,20 +7420,19 @@
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2839
+          <t xml:space="preserve">838
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>625</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1362
+          <t xml:space="preserve">1862
 </t>
         </is>
       </c>
@@ -755,13 +755,13 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">817
+          <t xml:space="preserve">872
 </t>
         </is>
       </c>
@@ -773,7 +773,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -821,7 +821,7 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -833,7 +833,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
@@ -857,7 +857,7 @@
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -869,7 +869,7 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1818
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
@@ -894,11 +894,11 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2038
-</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
+          <t xml:space="preserve">4038
+</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">326
 </t>
@@ -942,7 +942,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -966,7 +966,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9090
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -1018,15 +1018,15 @@
 </t>
         </is>
       </c>
-      <c r="X5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">728
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1411
+          <t xml:space="preserve">71740
 </t>
         </is>
       </c>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">4223
 </t>
         </is>
       </c>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1846
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -1127,9 +1127,9 @@
 </t>
         </is>
       </c>
-      <c r="P6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">800
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1153,25 +1153,25 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="W6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166141
+          <t xml:space="preserve">664
 </t>
         </is>
       </c>
@@ -1208,25 +1208,25 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64725
+          <t xml:space="preserve">4725
 </t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">347
-</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">348
+</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
@@ -1244,13 +1244,13 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">479
+          <t xml:space="preserve">847
 </t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1320,7 +1320,7 @@
 </t>
         </is>
       </c>
-      <c r="V7" s="8" t="inlineStr">
+      <c r="V7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">295
 </t>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">2965
 </t>
         </is>
       </c>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">914
+          <t xml:space="preserve">974
 </t>
         </is>
       </c>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17812
+          <t xml:space="preserve">17832
 </t>
         </is>
       </c>
@@ -1540,13 +1540,13 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130 17
+          <t xml:space="preserve">230 8
 </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">659
+          <t xml:space="preserve">679
 </t>
         </is>
       </c>
@@ -1558,13 +1558,13 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -1594,31 +1594,31 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942
+          <t xml:space="preserve">4942
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11796
+          <t xml:space="preserve">1496
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">1219
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1551
+          <t xml:space="preserve">1357
 </t>
         </is>
       </c>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
@@ -1654,13 +1654,13 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3888
+          <t xml:space="preserve">37888
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
+          <t xml:space="preserve">416
 </t>
         </is>
       </c>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81885
+          <t xml:space="preserve">354
 </t>
         </is>
       </c>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -1721,11 +1721,16 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n"/>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11 1
+</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">200
@@ -1756,7 +1761,7 @@
 </t>
         </is>
       </c>
-      <c r="Q10" s="3" t="inlineStr">
+      <c r="Q10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">299
 </t>
@@ -1764,13 +1769,13 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">944
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
@@ -1798,9 +1803,9 @@
 </t>
         </is>
       </c>
-      <c r="X10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
@@ -1812,7 +1817,7 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -1831,7 +1836,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12656
+          <t xml:space="preserve">2656
 </t>
         </is>
       </c>
@@ -1867,7 +1872,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -1897,13 +1902,13 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9273
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
@@ -1921,11 +1926,11 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="S11" s="8" t="inlineStr">
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">298
 </t>
@@ -1933,7 +1938,7 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7206
+          <t xml:space="preserve">706
 </t>
         </is>
       </c>
@@ -1943,15 +1948,15 @@
 </t>
         </is>
       </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">721
-</t>
-        </is>
-      </c>
-      <c r="W11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271
+</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">949
 </t>
         </is>
       </c>
@@ -1963,13 +1968,13 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28940
+          <t xml:space="preserve">8940
 </t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -1988,13 +1993,13 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3471
+          <t xml:space="preserve">2421
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
@@ -2022,9 +2027,9 @@
 </t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2271
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -2046,20 +2051,21 @@
 </t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t>3505</t>
-        </is>
-      </c>
-      <c r="N12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
+          <t xml:space="preserve">9275
 </t>
         </is>
       </c>
@@ -2083,13 +2089,13 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">518
+          <t xml:space="preserve">598
 </t>
         </is>
       </c>
@@ -2125,7 +2131,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">817
 </t>
         </is>
       </c>
@@ -2162,7 +2168,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">866
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -2180,13 +2186,13 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -2238,15 +2244,15 @@
 </t>
         </is>
       </c>
-      <c r="S13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4274
+          <t xml:space="preserve">527
 </t>
         </is>
       </c>
@@ -2270,7 +2276,7 @@
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
@@ -2305,9 +2311,9 @@
 </t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">307
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">071
 </t>
         </is>
       </c>
@@ -2337,17 +2343,22 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="n"/>
+          <t xml:space="preserve">821
+</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">224
@@ -2414,9 +2425,9 @@
 </t>
         </is>
       </c>
-      <c r="W14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2116
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -2432,12 +2443,7 @@
 </t>
         </is>
       </c>
-      <c r="Z14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
+      <c r="Z14" s="3" t="n"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -2453,7 +2459,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2828
+          <t xml:space="preserve">3596
 </t>
         </is>
       </c>
@@ -2489,7 +2495,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -2499,9 +2505,9 @@
 </t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">517
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -2511,7 +2517,7 @@
 </t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">216
 </t>
@@ -2525,13 +2531,13 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">1002
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2585,13 +2591,13 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7381
+          <t xml:space="preserve">731
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1006
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -2610,7 +2616,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12912
+          <t xml:space="preserve">12212
 </t>
         </is>
       </c>
@@ -2622,13 +2628,12 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1055
-</t>
+          <t>12551</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1514
+          <t xml:space="preserve">1319
 </t>
         </is>
       </c>
@@ -2664,13 +2669,13 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11106
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1095
+          <t xml:space="preserve">1098
 </t>
         </is>
       </c>
@@ -2682,7 +2687,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24901
+          <t xml:space="preserve">14901
 </t>
         </is>
       </c>
@@ -2700,13 +2705,13 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">12219
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11362
+          <t xml:space="preserve">11361
 </t>
         </is>
       </c>
@@ -2773,7 +2778,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
@@ -2803,7 +2808,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -2813,9 +2818,9 @@
 </t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">060
 </t>
         </is>
       </c>
@@ -2839,7 +2844,7 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3980
+          <t xml:space="preserve">9280
 </t>
         </is>
       </c>
@@ -2851,7 +2856,7 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
@@ -2875,24 +2880,24 @@
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>063</t>
-        </is>
-      </c>
-      <c r="W17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
-      <c r="X17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">846
+          <t>83</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
@@ -2929,7 +2934,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
@@ -2939,18 +2944,13 @@
 </t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">861
-</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n"/>
       <c r="H18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">804
@@ -2965,13 +2965,13 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
-        </is>
-      </c>
-      <c r="K18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">064
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -2987,15 +2987,15 @@
 </t>
         </is>
       </c>
-      <c r="N18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">913
+          <t xml:space="preserve">973
 </t>
         </is>
       </c>
@@ -3011,7 +3011,7 @@
 </t>
         </is>
       </c>
-      <c r="R18" s="8" t="inlineStr">
+      <c r="R18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">252
 </t>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">380
 </t>
         </is>
       </c>
@@ -3055,13 +3055,13 @@
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">714
+          <t xml:space="preserve">719
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -3108,9 +3108,9 @@
 </t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">914
 </t>
         </is>
       </c>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">806
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">511
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
@@ -3192,33 +3192,33 @@
 </t>
         </is>
       </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">163
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="W19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2898
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8290
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1859
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38659
+          <t xml:space="preserve">3659
 </t>
         </is>
       </c>
@@ -3247,15 +3247,15 @@
 </t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">081
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9280
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
@@ -3331,9 +3331,9 @@
 </t>
         </is>
       </c>
-      <c r="S20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">275
+      <c r="S20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -3355,27 +3355,27 @@
 </t>
         </is>
       </c>
-      <c r="W20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
+          <t xml:space="preserve">7250
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -3398,9 +3398,9 @@
 </t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">307
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">072
 </t>
         </is>
       </c>
@@ -3454,13 +3454,13 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="W21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">466
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7123
+          <t xml:space="preserve">723
 </t>
         </is>
       </c>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -3659,13 +3659,13 @@
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="V22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">865
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
@@ -3675,9 +3675,9 @@
 </t>
         </is>
       </c>
-      <c r="X22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">294
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12449
+          <t xml:space="preserve">1449
 </t>
         </is>
       </c>
@@ -3708,30 +3708,30 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>85196</t>
+          <t xml:space="preserve">17396
+</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14685
+          <t xml:space="preserve">1675
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10742
+          <t xml:space="preserve">1072
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1324
-</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">503
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -3749,12 +3749,12 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>104</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>491</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15657
+          <t xml:space="preserve">1557
 </t>
         </is>
       </c>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33251
+          <t xml:space="preserve">3251
 </t>
         </is>
       </c>
@@ -3819,13 +3819,13 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1384
+          <t xml:space="preserve">1344
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1203
+          <t xml:space="preserve">0203
 </t>
         </is>
       </c>
@@ -3843,8 +3843,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
+          <t>3625</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3862,7 +3861,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3879,7 +3878,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
@@ -3897,7 +3896,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3909,7 +3908,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -3951,13 +3950,13 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">856
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
@@ -3985,21 +3984,20 @@
 </t>
         </is>
       </c>
-      <c r="X24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
+          <t>29813</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">73
 </t>
         </is>
       </c>
@@ -4036,13 +4034,13 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -4066,7 +4064,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -4090,7 +4088,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9140
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
@@ -4108,7 +4106,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">841
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
@@ -4126,18 +4124,23 @@
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="n"/>
+          <t xml:space="preserve">53
+</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">228
 </t>
         </is>
       </c>
-      <c r="X25" s="8" t="inlineStr">
+      <c r="X25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">268
 </t>
@@ -4145,7 +4148,7 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84174
+          <t xml:space="preserve">87817
 </t>
         </is>
       </c>
@@ -4177,7 +4180,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -4189,7 +4192,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -4201,13 +4204,13 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">041
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -4231,7 +4234,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -4255,7 +4258,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
@@ -4267,7 +4270,7 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">1920
 </t>
         </is>
       </c>
@@ -4289,9 +4292,9 @@
 </t>
         </is>
       </c>
-      <c r="X26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">711
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
@@ -4303,7 +4306,7 @@
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -4328,7 +4331,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -4339,8 +4342,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -4375,7 +4377,7 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>504</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -4408,9 +4410,9 @@
 </t>
         </is>
       </c>
-      <c r="R27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -4432,21 +4434,21 @@
 </t>
         </is>
       </c>
-      <c r="V27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">869
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8269
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">944
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="X27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2890
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -4458,7 +4460,7 @@
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -4481,9 +4483,9 @@
 </t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">918
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
@@ -4549,13 +4551,13 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">973
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -4615,7 +4617,7 @@
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1074
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -4638,21 +4640,21 @@
 </t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">205
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">315
+</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0805
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
@@ -4676,7 +4678,7 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4718,7 +4720,7 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -4736,13 +4738,13 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8210
+          <t xml:space="preserve">8270
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">942
 </t>
         </is>
       </c>
@@ -4760,7 +4762,7 @@
       </c>
       <c r="X29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -4797,7 +4799,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11452
+          <t xml:space="preserve">1452
 </t>
         </is>
       </c>
@@ -4809,7 +4811,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11242
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
@@ -4821,7 +4823,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1966
+          <t xml:space="preserve">2966
 </t>
         </is>
       </c>
@@ -4839,7 +4841,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">3288
 </t>
         </is>
       </c>
@@ -4857,7 +4859,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
@@ -4881,13 +4883,13 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1201
+          <t xml:space="preserve">1207
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1409
+          <t xml:space="preserve">12409
 </t>
         </is>
       </c>
@@ -4897,27 +4899,22 @@
 </t>
         </is>
       </c>
-      <c r="U30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
+      <c r="U30" s="3" t="n"/>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11261
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1329
+          <t xml:space="preserve">1359
 </t>
         </is>
       </c>
@@ -4929,7 +4926,7 @@
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">858
 </t>
         </is>
       </c>
@@ -4954,18 +4951,18 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">086
-</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">906
+</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -4995,7 +4992,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 0
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
@@ -5019,7 +5016,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
+          <t xml:space="preserve">9275
 </t>
         </is>
       </c>
@@ -5055,7 +5052,7 @@
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -5073,19 +5070,19 @@
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">972
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">849
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
@@ -5104,7 +5101,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88169
+          <t xml:space="preserve">3847
 </t>
         </is>
       </c>
@@ -5116,13 +5113,13 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -5140,7 +5137,7 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -5170,7 +5167,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -5198,9 +5195,9 @@
 </t>
         </is>
       </c>
-      <c r="S32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">725
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -5212,31 +5209,30 @@
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">838
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">972
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">761
+          <t xml:space="preserve">76416
 </t>
         </is>
       </c>
@@ -5315,7 +5311,7 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -5327,7 +5323,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -5345,13 +5341,13 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -5363,7 +5359,7 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">709
 </t>
         </is>
       </c>
@@ -5379,7 +5375,7 @@
 </t>
         </is>
       </c>
-      <c r="W33" s="8" t="inlineStr">
+      <c r="W33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">238
 </t>
@@ -5393,13 +5389,12 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">1445
 </t>
         </is>
       </c>
@@ -5434,7 +5429,7 @@
 </t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">267
 </t>
@@ -5442,7 +5437,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -5460,7 +5455,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">395
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -5502,13 +5497,13 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -5550,7 +5545,7 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
@@ -5579,7 +5574,7 @@
 </t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">311
 </t>
@@ -5587,11 +5582,10 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
+          <t>308</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">259
 </t>
@@ -5653,7 +5647,7 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">071
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -5663,36 +5657,36 @@
 </t>
         </is>
       </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
+      <c r="R35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">469
 </t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">613
+</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">278
 </t>
         </is>
       </c>
-      <c r="T35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">613
-</t>
-        </is>
-      </c>
-      <c r="U35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="V35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
       <c r="W35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">166
@@ -5707,13 +5701,12 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">779
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8111
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -5804,7 +5797,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
+          <t xml:space="preserve">975
 </t>
         </is>
       </c>
@@ -5850,27 +5843,27 @@
 </t>
         </is>
       </c>
-      <c r="W36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="X36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">839
+      <c r="W36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">466
+</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1720
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">14110
 </t>
         </is>
       </c>
@@ -5949,13 +5942,13 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1052
+          <t xml:space="preserve">1032
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
@@ -5973,7 +5966,7 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
+          <t xml:space="preserve">1537
 </t>
         </is>
       </c>
@@ -5991,19 +5984,19 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82168
+          <t xml:space="preserve">3248
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">1368
 </t>
         </is>
       </c>
@@ -6015,19 +6008,19 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1024
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3982
+          <t xml:space="preserve">39282
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8921
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
@@ -6076,7 +6069,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -6129,7 +6122,7 @@
 </t>
         </is>
       </c>
-      <c r="R38" s="8" t="inlineStr">
+      <c r="R38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">252
 </t>
@@ -6143,19 +6136,19 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">690
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -6179,7 +6172,7 @@
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5661
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -6198,13 +6191,13 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32325
-</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82181
+          <t xml:space="preserve">3325
+</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -6226,7 +6219,7 @@
 </t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">193
 </t>
@@ -6246,7 +6239,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -6282,11 +6275,11 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="R39" s="8" t="inlineStr">
+          <t xml:space="preserve">919
+</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">260
 </t>
@@ -6306,19 +6299,19 @@
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">491
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -6336,7 +6329,7 @@
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
@@ -6355,13 +6348,13 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15341
+          <t xml:space="preserve">1537
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -6391,13 +6384,13 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -6457,7 +6450,7 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">392
+          <t xml:space="preserve">592
 </t>
         </is>
       </c>
@@ -6473,21 +6466,21 @@
 </t>
         </is>
       </c>
-      <c r="W40" s="8" t="inlineStr">
+      <c r="W40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">238
 </t>
         </is>
       </c>
-      <c r="X40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
+      <c r="X40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">869
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
@@ -6512,7 +6505,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9656
+          <t xml:space="preserve">89856
 </t>
         </is>
       </c>
@@ -6583,73 +6576,73 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="S41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">923
+</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">980
 </t>
         </is>
       </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="T41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">929
-</t>
-        </is>
-      </c>
-      <c r="U41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="V41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">466
-</t>
-        </is>
-      </c>
-      <c r="W41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="X41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92180
-</t>
-        </is>
-      </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">905
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -6678,9 +6671,9 @@
 </t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">039
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -6690,7 +6683,7 @@
 </t>
         </is>
       </c>
-      <c r="G42" s="8" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">113
 </t>
@@ -6708,15 +6701,15 @@
 </t>
         </is>
       </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="K42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">080
+</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
@@ -6734,13 +6727,13 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18990
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -6780,21 +6773,21 @@
 </t>
         </is>
       </c>
-      <c r="V42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8229
-</t>
-        </is>
-      </c>
-      <c r="W42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">825
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="X42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">8282
 </t>
         </is>
       </c>
@@ -6843,127 +6836,127 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">291
 </t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">804
+</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">756
+</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">291
 </t>
         </is>
       </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">804
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">756
-</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="W43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">414
-</t>
-        </is>
-      </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">780
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1982
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -6982,13 +6975,13 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">659
+          <t xml:space="preserve">3659
 </t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">226 1
 </t>
         </is>
       </c>
@@ -7010,9 +7003,9 @@
 </t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">894
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -7034,15 +7027,15 @@
 </t>
         </is>
       </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
+      <c r="L44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">823
 </t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">823
 </t>
         </is>
       </c>
@@ -7060,7 +7053,7 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -7070,7 +7063,7 @@
 </t>
         </is>
       </c>
-      <c r="R44" s="8" t="inlineStr">
+      <c r="R44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">264
 </t>
@@ -7078,25 +7071,25 @@
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">806
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">086
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
@@ -7106,9 +7099,9 @@
 </t>
         </is>
       </c>
-      <c r="X44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">828
+      <c r="X44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -7145,37 +7138,37 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191656
+          <t xml:space="preserve">19016
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11280
+          <t xml:space="preserve">112986
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20261
+          <t xml:space="preserve">2261
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">091
+          <t xml:space="preserve">021
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11142
+          <t xml:space="preserve">111 42
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11010
+          <t xml:space="preserve">0110
 </t>
         </is>
       </c>
@@ -7187,18 +7180,18 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>7836</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116659
+          <t xml:space="preserve">11665
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
@@ -7210,13 +7203,13 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2928
+          <t xml:space="preserve">2938
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -7228,25 +7221,25 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">014691
+          <t xml:space="preserve">1491
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1741
+          <t xml:space="preserve">1211
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14508
+          <t xml:space="preserve">12300
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">656
+          <t xml:space="preserve">686
 </t>
         </is>
       </c>
@@ -7258,24 +7251,24 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1282
+</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1722
 </t>
         </is>
       </c>
-      <c r="X45" s="3" t="inlineStr">
-        <is>
-          <t>845</t>
-        </is>
-      </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9001
-</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">560
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -7316,7 +7309,7 @@
 </t>
         </is>
       </c>
-      <c r="G46" s="8" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">215
 </t>
@@ -7340,15 +7333,10 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="L46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
+      <c r="K46" s="3" t="n"/>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -7366,7 +7354,7 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
@@ -7396,7 +7384,7 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">729
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -7426,13 +7414,13 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,13 +737,13 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1862
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
@@ -761,19 +761,19 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
-</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -785,7 +785,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -861,7 +861,7 @@
 </t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
+      <c r="X4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">262
 </t>
@@ -894,7 +894,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4038
+          <t xml:space="preserve">2403
 </t>
         </is>
       </c>
@@ -922,9 +922,9 @@
 </t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4168
 </t>
         </is>
       </c>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71740
+          <t xml:space="preserve">770
 </t>
         </is>
       </c>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -1079,15 +1079,15 @@
 </t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">1558
 </t>
         </is>
       </c>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -1224,9 +1224,9 @@
 </t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">720
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">847
+          <t xml:space="preserve">647
 </t>
         </is>
       </c>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -1310,19 +1310,19 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">506
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -1407,11 +1407,11 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">309
 </t>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2965
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17832
+          <t xml:space="preserve">1783
 </t>
         </is>
       </c>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230 8
+          <t xml:space="preserve">1308
 </t>
         </is>
       </c>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -1570,8 +1570,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -1588,19 +1587,19 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4942
+          <t xml:space="preserve">4945
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1624,13 +1623,13 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3299
+          <t xml:space="preserve">23299
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -1654,7 +1653,7 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37888
+          <t xml:space="preserve">3888
 </t>
         </is>
       </c>
@@ -1679,7 +1678,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">354
+          <t xml:space="preserve">3567
 </t>
         </is>
       </c>
@@ -1691,7 +1690,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -1725,12 +1724,7 @@
 </t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11 1
-</t>
-        </is>
-      </c>
+      <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">200
@@ -1761,7 +1755,7 @@
 </t>
         </is>
       </c>
-      <c r="Q10" s="8" t="inlineStr">
+      <c r="Q10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">299
 </t>
@@ -1811,7 +1805,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">778
 </t>
         </is>
       </c>
@@ -1872,52 +1866,52 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">973
+</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">06
 </t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">245
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">299
@@ -1926,7 +1920,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -1956,7 +1950,7 @@
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -1968,13 +1962,13 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">1598
 </t>
         </is>
       </c>
@@ -1993,19 +1987,19 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2421
+          <t xml:space="preserve">3471
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -2035,7 +2029,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -2065,7 +2059,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9275
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -2095,7 +2089,7 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
+          <t xml:space="preserve">588
 </t>
         </is>
       </c>
@@ -2107,7 +2101,7 @@
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
@@ -2131,7 +2125,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">817
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -2162,7 +2156,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -2192,7 +2186,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2270,7 +2264,7 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -2288,7 +2282,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -2311,9 +2305,9 @@
 </t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">071
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
@@ -2343,13 +2337,13 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -2391,7 +2385,7 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -2403,8 +2397,7 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
@@ -2443,7 +2436,12 @@
 </t>
         </is>
       </c>
-      <c r="Z14" s="3" t="n"/>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -2507,31 +2505,31 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">216
 </t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1002
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
@@ -2616,30 +2614,31 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12212
+          <t xml:space="preserve">15912
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1679
+          <t xml:space="preserve">1579
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>12551</t>
+          <t xml:space="preserve">1055
+</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1319
+          <t xml:space="preserve">1317
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">524
+          <t xml:space="preserve">3524
 </t>
         </is>
       </c>
@@ -2669,25 +2668,25 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
+          <t xml:space="preserve">11106
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1098
+          <t xml:space="preserve">1095
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12307
+          <t xml:space="preserve">1307
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14901
+          <t xml:space="preserve">24901
 </t>
         </is>
       </c>
@@ -2705,7 +2704,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12219
+          <t xml:space="preserve">1219
 </t>
         </is>
       </c>
@@ -2735,7 +2734,7 @@
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">21207
 </t>
         </is>
       </c>
@@ -2747,14 +2746,13 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14076
+          <t xml:space="preserve">4074
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
-</t>
+          <t>344</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2776,7 +2774,7 @@
 </t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">316
 </t>
@@ -2818,9 +2816,9 @@
 </t>
         </is>
       </c>
-      <c r="K17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">060
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -2844,13 +2842,13 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9280
+          <t xml:space="preserve">2980
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2874,7 +2872,7 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">664
+          <t xml:space="preserve">1664
 </t>
         </is>
       </c>
@@ -2886,10 +2884,11 @@
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="W17" s="3" t="inlineStr">
+          <t xml:space="preserve">267
+</t>
+        </is>
+      </c>
+      <c r="W17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">241
 </t>
@@ -2909,7 +2908,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -2946,14 +2945,19 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="n"/>
+          <t xml:space="preserve">267
+</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -2965,20 +2969,18 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -2995,7 +2997,7 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">973
+          <t xml:space="preserve">1973
 </t>
         </is>
       </c>
@@ -3005,7 +3007,7 @@
 </t>
         </is>
       </c>
-      <c r="Q18" s="3" t="inlineStr">
+      <c r="Q18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">321
 </t>
@@ -3025,7 +3027,7 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -3043,19 +3045,18 @@
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
+          <t xml:space="preserve">1717
 </t>
         </is>
       </c>
@@ -3108,9 +3109,9 @@
 </t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">914
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -3158,7 +3159,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -3198,9 +3199,9 @@
 </t>
         </is>
       </c>
-      <c r="W19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">289
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -3218,7 +3219,7 @@
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -3241,27 +3242,27 @@
 </t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">314
 </t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -3279,7 +3280,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -3303,7 +3304,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
@@ -3315,7 +3316,7 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -3331,15 +3332,15 @@
 </t>
         </is>
       </c>
-      <c r="S20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">175
+      <c r="S20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">623
 </t>
         </is>
       </c>
@@ -3351,13 +3352,13 @@
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -3369,13 +3370,13 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7250
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -3398,9 +3399,9 @@
 </t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">072
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
@@ -3512,9 +3513,9 @@
 </t>
         </is>
       </c>
-      <c r="W21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -3551,7 +3552,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3993
+          <t xml:space="preserve">23993
 </t>
         </is>
       </c>
@@ -3575,7 +3576,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -3599,7 +3600,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
@@ -3623,13 +3624,13 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">014
 </t>
         </is>
       </c>
@@ -3641,7 +3642,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -3663,7 +3664,7 @@
 </t>
         </is>
       </c>
-      <c r="V22" s="8" t="inlineStr">
+      <c r="V22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">265
 </t>
@@ -3689,7 +3690,7 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1449
+          <t xml:space="preserve">649
 </t>
         </is>
       </c>
@@ -3714,7 +3715,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1675
+          <t xml:space="preserve">1575
 </t>
         </is>
       </c>
@@ -3726,12 +3727,13 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t xml:space="preserve">1324
+</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">503
 </t>
         </is>
       </c>
@@ -3749,12 +3751,14 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t xml:space="preserve">193
+</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>491</t>
+          <t xml:space="preserve">193
+</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -3765,7 +3769,7 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11070
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -3807,14 +3811,13 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3251
+          <t xml:space="preserve">3257
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">794
-</t>
+          <t>724</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
@@ -3825,7 +3828,7 @@
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0203
+          <t xml:space="preserve">11203
 </t>
         </is>
       </c>
@@ -3843,7 +3846,8 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t xml:space="preserve">367
+</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3861,7 +3865,8 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>3432</t>
+          <t xml:space="preserve">3479
+</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3878,7 +3883,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
@@ -3906,12 +3911,7 @@
 </t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">216
@@ -3950,13 +3950,13 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
@@ -3986,18 +3986,19 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>29813</t>
+          <t xml:space="preserve">798
+</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -4032,7 +4033,7 @@
 </t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">235
 </t>
@@ -4076,8 +4077,7 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>981</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -4124,13 +4124,13 @@
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -4148,11 +4148,16 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87817
-</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="n"/>
+          <t xml:space="preserve">877
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -4180,7 +4185,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -4216,7 +4221,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
@@ -4270,13 +4275,13 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4300,13 +4305,13 @@
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0918
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -4331,7 +4336,8 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>305</t>
+          <t xml:space="preserve">205
+</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -4342,12 +4348,13 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>255</t>
+          <t xml:space="preserve">255
+</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -4377,7 +4384,8 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>504</t>
+          <t xml:space="preserve">207
+</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -4394,7 +4402,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">2980
 </t>
         </is>
       </c>
@@ -4424,7 +4432,7 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">732
 </t>
         </is>
       </c>
@@ -4434,9 +4442,9 @@
 </t>
         </is>
       </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8269
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -4446,9 +4454,9 @@
 </t>
         </is>
       </c>
-      <c r="X27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">890
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -4460,7 +4468,7 @@
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -4485,7 +4493,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -4551,13 +4559,13 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">973
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -4575,7 +4583,7 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -4646,9 +4654,9 @@
 </t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0805
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -4658,15 +4666,15 @@
 </t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">110
 </t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">692
 </t>
         </is>
       </c>
@@ -4690,7 +4698,7 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -4708,7 +4716,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4720,7 +4728,7 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
@@ -4738,13 +4746,13 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8270
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
@@ -4760,16 +4768,15 @@
 </t>
         </is>
       </c>
-      <c r="X29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
-</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
@@ -4793,7 +4800,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110562
+          <t xml:space="preserve">10562
 </t>
         </is>
       </c>
@@ -4835,13 +4842,13 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3288
+          <t xml:space="preserve">388
 </t>
         </is>
       </c>
@@ -4865,7 +4872,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4876
+          <t xml:space="preserve">24876
 </t>
         </is>
       </c>
@@ -4889,7 +4896,7 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12409
+          <t xml:space="preserve">1409
 </t>
         </is>
       </c>
@@ -4899,10 +4906,15 @@
 </t>
         </is>
       </c>
-      <c r="U30" s="3" t="n"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">11261
 </t>
         </is>
       </c>
@@ -4920,13 +4932,13 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14247
+          <t xml:space="preserve">14287
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -4951,16 +4963,17 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t xml:space="preserve">290
+</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">248
 </t>
@@ -4990,12 +5003,7 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9
-</t>
-        </is>
-      </c>
+      <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">213
@@ -5016,7 +5024,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9275
+          <t xml:space="preserve">975
 </t>
         </is>
       </c>
@@ -5052,17 +5060,17 @@
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="V31" s="3" t="inlineStr">
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">252
 </t>
         </is>
       </c>
-      <c r="W31" s="3" t="inlineStr">
+      <c r="W31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">232
 </t>
@@ -5076,7 +5084,7 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">849
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -5113,13 +5121,13 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -5167,7 +5175,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -5215,12 +5223,13 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t xml:space="preserve">274
+</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -5232,13 +5241,13 @@
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76416
+          <t xml:space="preserve">7466
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">1953
 </t>
         </is>
       </c>
@@ -5261,9 +5270,9 @@
 </t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2292
 </t>
         </is>
       </c>
@@ -5293,7 +5302,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -5305,7 +5314,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -5323,7 +5332,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -5347,7 +5356,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -5389,12 +5398,12 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1445
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -5417,7 +5426,7 @@
 </t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">319
 </t>
@@ -5455,7 +5464,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -5485,7 +5494,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
@@ -5501,9 +5510,9 @@
 </t>
         </is>
       </c>
-      <c r="R34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
+      <c r="R34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">358
 </t>
         </is>
       </c>
@@ -5545,7 +5554,7 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -5570,7 +5579,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3534
+          <t xml:space="preserve">3531
 </t>
         </is>
       </c>
@@ -5582,7 +5591,8 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>308</t>
+          <t xml:space="preserve">208
+</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -5641,7 +5651,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">972
+          <t xml:space="preserve">2972
 </t>
         </is>
       </c>
@@ -5665,7 +5675,7 @@
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -5701,7 +5711,8 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t xml:space="preserve">776
+</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
@@ -5747,7 +5758,7 @@
 </t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">112
 </t>
@@ -5797,8 +5808,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>9251</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -5843,27 +5853,27 @@
 </t>
         </is>
       </c>
-      <c r="W36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">466
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
+          <t xml:space="preserve">1720
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14110
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
@@ -5888,13 +5898,13 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1554
+          <t xml:space="preserve">141554
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
+          <t xml:space="preserve">102 0
 </t>
         </is>
       </c>
@@ -5918,7 +5928,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
+          <t xml:space="preserve">11 01
 </t>
         </is>
       </c>
@@ -5942,7 +5952,7 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1032
+          <t xml:space="preserve">1052
 </t>
         </is>
       </c>
@@ -5960,7 +5970,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17 1
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -5978,19 +5988,19 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1431
+          <t xml:space="preserve">11431
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3248
+          <t xml:space="preserve">23248
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">797
 </t>
         </is>
       </c>
@@ -6014,13 +6024,13 @@
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39282
+          <t xml:space="preserve">3922
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">397
+          <t xml:space="preserve">1397
 </t>
         </is>
       </c>
@@ -6045,7 +6055,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -6106,7 +6116,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -6136,7 +6146,7 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
+          <t xml:space="preserve">650
 </t>
         </is>
       </c>
@@ -6148,7 +6158,7 @@
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
@@ -6160,13 +6170,13 @@
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
@@ -6213,13 +6223,13 @@
 </t>
         </is>
       </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="H39" s="8" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">193
 </t>
@@ -6239,7 +6249,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
@@ -6275,7 +6285,7 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -6299,13 +6309,13 @@
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
@@ -6317,7 +6327,7 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -6329,7 +6339,7 @@
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -6348,13 +6358,13 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1537
+          <t xml:space="preserve">14537
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
@@ -6472,9 +6482,9 @@
 </t>
         </is>
       </c>
-      <c r="X40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">869
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -6486,7 +6496,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1016
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -6505,11 +6515,11 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89856
-</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
+          <t xml:space="preserve">2656
+</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">316
 </t>
@@ -6521,7 +6531,7 @@
 </t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">256
 </t>
@@ -6553,7 +6563,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
@@ -6598,9 +6608,9 @@
 </t>
         </is>
       </c>
-      <c r="S41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -6616,9 +6626,9 @@
 </t>
         </is>
       </c>
-      <c r="V41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
+      <c r="V41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -6630,19 +6640,19 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
+          <t xml:space="preserve">1905
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -6661,7 +6671,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8363
+          <t xml:space="preserve">2363
 </t>
         </is>
       </c>
@@ -6701,15 +6711,15 @@
 </t>
         </is>
       </c>
-      <c r="J42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">080
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -6763,31 +6773,31 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">977
+          <t xml:space="preserve">972
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="X42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8282
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -6797,12 +6807,7 @@
 </t>
         </is>
       </c>
-      <c r="Z42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
+      <c r="Z42" s="3" t="n"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -6836,116 +6841,115 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">291
+</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">804
+</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">756
+</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">278
+</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">247
 </t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">37
-</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">804
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">756
-</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>341</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
@@ -6981,7 +6985,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226 1
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -7005,7 +7009,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">0494
 </t>
         </is>
       </c>
@@ -7017,7 +7021,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -7027,15 +7031,15 @@
 </t>
         </is>
       </c>
-      <c r="L44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">823
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">823
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -7089,7 +7093,7 @@
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -7099,15 +7103,15 @@
 </t>
         </is>
       </c>
-      <c r="X44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">1844
 </t>
         </is>
       </c>
@@ -7132,72 +7136,72 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20262
+          <t xml:space="preserve">2026
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19016
+          <t xml:space="preserve">1906
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112986
+          <t xml:space="preserve">11215
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2261
-</t>
+          <t>1563</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">021
+          <t xml:space="preserve">691
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111 42
+          <t xml:space="preserve">11147
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0110
+          <t xml:space="preserve">1012
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>7836</t>
+          <t xml:space="preserve">183
+</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11665
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">101229
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11488
+          <t xml:space="preserve">11487
 </t>
         </is>
       </c>
@@ -7227,13 +7231,13 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1211
+          <t xml:space="preserve">1741
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12300
+          <t xml:space="preserve">24300
 </t>
         </is>
       </c>
@@ -7251,7 +7255,7 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">1449
 </t>
         </is>
       </c>
@@ -7263,12 +7267,13 @@
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t xml:space="preserve">5837
+</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
@@ -7291,7 +7296,7 @@
 </t>
         </is>
       </c>
-      <c r="D46" s="8" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">317
 </t>
@@ -7311,7 +7316,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -7333,7 +7338,12 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="n"/>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">211
@@ -7342,7 +7352,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -7354,7 +7364,7 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -7364,7 +7374,7 @@
 </t>
         </is>
       </c>
-      <c r="Q46" s="3" t="inlineStr">
+      <c r="Q46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">288
 </t>
@@ -7384,7 +7394,7 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">750
 </t>
         </is>
       </c>
@@ -7414,13 +7424,14 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">8239
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t xml:space="preserve">57
+</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_digit_manipulation.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -107,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -122,9 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -737,146 +728,122 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">882
-</t>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>182</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
-</t>
+          <t>689</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="X4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-</t>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>262</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>818</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -894,146 +861,122 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2403
-</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4168
-</t>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">566
-</t>
+          <t>566</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1051,146 +994,122 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
-</t>
+          <t>342</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
-</t>
+          <t>327</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1558
-</t>
+          <t>558</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">664
-</t>
+          <t>664</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1208,146 +1127,122 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4725
-</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>347</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">647
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
-</t>
+          <t>342</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">506
-</t>
+          <t>506</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1365,146 +1260,122 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2990
-</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">346
-</t>
+          <t>346</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>190</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">309
-</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>309</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
-</t>
+          <t>974</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1522,50 +1393,42 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1783
-</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1648
-</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">969
-</t>
+          <t>969</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1308
-</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">679
-</t>
+          <t>679</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
-</t>
+          <t>894</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -1575,92 +1438,77 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1002
-</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4945
-</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1496
-</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
-</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1357
-</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23299
-</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1328
-</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1335
-</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3888
-</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">416
-</t>
+          <t>416</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1678,141 +1526,118 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3567
-</t>
+          <t>3567</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
-</t>
+          <t>989</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
+          <t>660</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1830,146 +1655,122 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2656
-</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">973
-</t>
+          <t>973</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">706
-</t>
+          <t>706</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1598
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1987,146 +1788,122 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3471
-</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
-</t>
+          <t>578</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">767
-</t>
+          <t>767</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2144,146 +1921,122 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4286
-</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">527
-</t>
+          <t>527</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">776
-</t>
+          <t>776</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2301,98 +2054,82 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903
-</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">973
-</t>
+          <t>973</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -2402,44 +2139,37 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
-</t>
+          <t>960</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2457,146 +2187,122 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3596
-</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
+          <t>325</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
-</t>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>117</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>320</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">617
-</t>
+          <t>617</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">731
-</t>
+          <t>731</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2614,140 +2320,117 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15912
-</t>
+          <t>15912</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1579
-</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1055
-</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1317
-</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3524
-</t>
+          <t>524</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
-</t>
+          <t>992</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">368
-</t>
+          <t>368</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11106
-</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1095
-</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1307
-</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24901
-</t>
+          <t>4901</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1487
-</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
-</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11361
-</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3318
-</t>
+          <t>3318</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">766
-</t>
+          <t>766</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1337
-</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21207
-</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1425
-</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4074
-</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2770,146 +2453,122 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3182
-</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">316
-</t>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>316</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664
-</t>
+          <t>664</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
-        </is>
-      </c>
-      <c r="W17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>241</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
-</t>
+          <t>815</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2927,50 +2586,42 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3680
-</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -2985,62 +2636,52 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1973
-</t>
+          <t>973</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321
-</t>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>321</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
@@ -3050,20 +2691,17 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1717
-</t>
+          <t>717</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -3081,146 +2719,122 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2656
-</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">976
-</t>
+          <t>976</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">299
-</t>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>299</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">737
-</t>
+          <t>737</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3238,146 +2852,122 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3659
-</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">314
-</t>
+          <t>3659</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>314</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">265
-</t>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>265</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">623
-</t>
+          <t>623</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>750</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3395,146 +2985,122 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3408
-</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">712
-</t>
+          <t>712</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
-</t>
+          <t>773</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3552,146 +3118,122 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23993
-</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>329</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">014
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">893
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
-</t>
+          <t>605</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">649
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3709,110 +3251,92 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17396
-</t>
+          <t>17396</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1575
-</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
-</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1324
-</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">503
-</t>
+          <t>503</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1018
-</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1082
-</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
-</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4894
-</t>
+          <t>894</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1557
-</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
-</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1468
-</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3257
-</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
@@ -3822,32 +3346,27 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1344
-</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11203
-</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1408
-</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3990
-</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">367
-</t>
+          <t>367</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3865,141 +3384,118 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3479
-</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
-</t>
+          <t>315</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">979
-</t>
+          <t>979</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">651
-</t>
+          <t>651</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -4017,62 +3513,52 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1067
-</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235
-</t>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>235</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -4082,80 +3568,67 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
-</t>
+          <t>844</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">877
-</t>
+          <t>877</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4173,146 +3646,122 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
-</t>
+          <t>918</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4330,146 +3779,122 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
-</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
-</t>
+          <t>732</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>818</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4487,146 +3912,122 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2907
-</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>113</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">973
-</t>
+          <t>973</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
-</t>
+          <t>602</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">726
-</t>
+          <t>726</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4644,134 +4045,112 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2468
-</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
-</t>
+          <t>315</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">692
-</t>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>192</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>953</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -4781,8 +4160,7 @@
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4800,146 +4178,122 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10562
-</t>
+          <t>10562</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1452
-</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1032
-</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
-</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
-</t>
+          <t>420</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2966
-</t>
+          <t>966</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">388
-</t>
+          <t>388</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1065
-</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1052
-</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
-</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24876
-</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11358
-</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
-</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1409
-</t>
+          <t>1409</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3968
-</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11261
-</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
-</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1359
-</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14287
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4957,141 +4311,118 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2112
-</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>248</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">794
-</t>
+          <t>794</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="W31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>232</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>849</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5109,146 +4440,122 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3847
-</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="H32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>180</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7466
-</t>
+          <t>746</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1953
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -5266,134 +4573,112 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2133
-</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2292
-</t>
+          <t>2133</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>292</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>997</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">709
-</t>
+          <t>709</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -5403,8 +4688,7 @@
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5422,146 +4706,122 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3116
-</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
-        </is>
-      </c>
-      <c r="R34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">358
-</t>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>258</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
-</t>
+          <t>694</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5579,146 +4839,122 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3531
-</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311
-</t>
+          <t>3534</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>311</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2972
-</t>
+          <t>972</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
-        </is>
-      </c>
-      <c r="R35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">469
-</t>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>249</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">613
-</t>
+          <t>613</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
-        </is>
-      </c>
-      <c r="W35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>246</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">776
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5736,74 +4972,62 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -5813,68 +5037,57 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">622
-</t>
+          <t>622</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1720
-</t>
+          <t>720</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5892,146 +5105,122 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16937
-</t>
+          <t>16937</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141554
-</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102 0
-</t>
+          <t>102 2</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1287
-</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">534
-</t>
+          <t>534</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 01
-</t>
+          <t>11 01</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
-</t>
+          <t>356</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11060
-</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1052
-</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
-</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4927
-</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1537
-</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
-</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11431
-</t>
+          <t>1431</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23248
-</t>
+          <t>3248</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">797
-</t>
+          <t>777</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1368
-</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
-</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
-</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3922
-</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
-</t>
+          <t>397</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -6049,141 +5238,118 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3387
-</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>985</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">650
-</t>
+          <t>650</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>780</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -6201,146 +5367,122 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3325
-</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1632
-</t>
+          <t>632</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6358,146 +5500,122 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14537
-</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>329</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
+          <t>978</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
-</t>
+          <t>592</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
-</t>
+          <t>720</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6515,50 +5633,42 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2656
-</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">316
-</t>
+          <t>2656</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>316</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
@@ -6568,92 +5678,77 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
-</t>
+          <t>923</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="V41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>246</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1905
-</t>
+          <t>905</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6671,140 +5766,117 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2363
-</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
-</t>
+          <t>316</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">972
-</t>
+          <t>977</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
+          <t>906</t>
         </is>
       </c>
       <c r="Z42" s="3" t="n"/>
@@ -6823,128 +5895,107 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3722
-</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">756
-</t>
+          <t>756</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
@@ -6954,14 +6005,12 @@
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
-</t>
+          <t>780</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6979,146 +6028,122 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3659
-</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="H44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0494
-</t>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>194</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
-</t>
+          <t>620</t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1844
-</t>
+          <t>844</t>
         </is>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AA44" s="3" t="inlineStr">
@@ -7136,20 +6161,17 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026
-</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1906
-</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11215
-</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -7159,122 +6181,102 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
-</t>
+          <t>691</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11147
-</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1012
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>723</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
-</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101229
-</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11487
-</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2938
-</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
-</t>
+          <t>1728</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1491
-</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1741
-</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24300
-</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
-</t>
+          <t>686</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1581
-</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1449
-</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1722
-</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5837
-</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
-</t>
+          <t>340</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -7292,146 +6294,122 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2376
-</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
-</t>
+          <t>317</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>288</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">750
-</t>
+          <t>750</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8239
-</t>
+          <t>839</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_digit_manipulation.xlsx
@@ -994,7 +994,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>17835</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1564,7 +1564,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="K10" s="3" t="n"/>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t>200</t>
@@ -1793,7 +1797,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -3138,7 +3142,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>118 2</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3163,7 +3167,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>2213</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -3311,7 +3315,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -3731,7 +3735,7 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>282</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
@@ -3839,7 +3843,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3942,7 +3946,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>222</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -3977,7 +3981,7 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -4253,7 +4257,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1207 2</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -4268,7 +4272,7 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>260</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
@@ -4288,7 +4292,7 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4346,7 +4350,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>222</t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
@@ -4397,7 +4401,7 @@
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>181</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
@@ -4633,7 +4637,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
@@ -4648,7 +4652,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>246</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -4939,7 +4943,7 @@
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>266</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
@@ -4949,7 +4953,7 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>774</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
@@ -4972,7 +4976,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>4307</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -5115,7 +5119,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>102 2</t>
+          <t>102 0</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -5210,12 +5214,12 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
@@ -5344,7 +5348,7 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>784</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
@@ -5377,7 +5381,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -5407,7 +5411,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
@@ -5530,7 +5534,7 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -5801,7 +5805,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
@@ -5861,7 +5865,7 @@
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>247</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
@@ -6161,7 +6165,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>20262</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6171,7 +6175,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1215 2</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -6201,7 +6205,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>783</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
@@ -6246,7 +6250,7 @@
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
@@ -6334,7 +6338,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0 1</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6364,7 +6368,7 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>2288</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
@@ -6404,7 +6408,7 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>832</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_digit_manipulation.xlsx
@@ -994,7 +994,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>4223</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>06</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>17835</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>416</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1564,11 +1564,7 @@
           <t>55</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t>200</t>
@@ -2497,7 +2493,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -3142,7 +3138,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>118 2</t>
+          <t>168</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3167,7 +3163,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>213</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -3735,12 +3731,12 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>920</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>20</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
@@ -3843,7 +3839,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3946,7 +3942,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -4257,7 +4253,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>1207 2</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -4272,7 +4268,7 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>105</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
@@ -4315,7 +4311,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>211</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -4350,7 +4346,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
@@ -4401,7 +4397,7 @@
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>81</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
@@ -4943,7 +4939,7 @@
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>246</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
@@ -5139,7 +5135,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>11 01</t>
+          <t>1 01</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -5214,12 +5210,12 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
@@ -5381,7 +5377,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -5614,7 +5610,7 @@
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>780</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
@@ -6165,7 +6161,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>20262</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6175,7 +6171,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>1215 2</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -6338,7 +6334,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>0 1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6368,7 +6364,7 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>288</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
@@ -6408,7 +6404,7 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>839</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
